--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122178285</v>
+        <v>122178276</v>
       </c>
       <c r="B6" t="n">
-        <v>98196</v>
+        <v>78645</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,25 +1161,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478533</v>
+        <v>478356</v>
       </c>
       <c r="R6" t="n">
-        <v>6950174</v>
+        <v>6950124</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122178280</v>
+        <v>122178272</v>
       </c>
       <c r="B7" t="n">
-        <v>98196</v>
+        <v>97129</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478460</v>
+        <v>478246</v>
       </c>
       <c r="R7" t="n">
-        <v>6950137</v>
+        <v>6950307</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122178281</v>
+        <v>122178279</v>
       </c>
       <c r="B8" t="n">
-        <v>98196</v>
+        <v>78645</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,25 +1365,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478481</v>
+        <v>478454</v>
       </c>
       <c r="R8" t="n">
-        <v>6950141</v>
+        <v>6950126</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122178284</v>
+        <v>122178286</v>
       </c>
       <c r="B9" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,25 +1467,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478499</v>
+        <v>478529</v>
       </c>
       <c r="R9" t="n">
-        <v>6950188</v>
+        <v>6950164</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122178283</v>
+        <v>122178273</v>
       </c>
       <c r="B10" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,25 +1569,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478488</v>
+        <v>478296</v>
       </c>
       <c r="R10" t="n">
-        <v>6950169</v>
+        <v>6950347</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122178279</v>
+        <v>122178285</v>
       </c>
       <c r="B11" t="n">
-        <v>78645</v>
+        <v>98196</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,25 +1671,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478454</v>
+        <v>478533</v>
       </c>
       <c r="R11" t="n">
-        <v>6950126</v>
+        <v>6950174</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122178273</v>
+        <v>122178282</v>
       </c>
       <c r="B12" t="n">
-        <v>78645</v>
+        <v>98196</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,25 +1773,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478296</v>
+        <v>478489</v>
       </c>
       <c r="R12" t="n">
-        <v>6950347</v>
+        <v>6950163</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122178272</v>
+        <v>122178281</v>
       </c>
       <c r="B13" t="n">
-        <v>97129</v>
+        <v>98196</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,21 +1879,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478246</v>
+        <v>478481</v>
       </c>
       <c r="R13" t="n">
-        <v>6950307</v>
+        <v>6950141</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122178278</v>
+        <v>122178274</v>
       </c>
       <c r="B14" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,25 +1977,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478422</v>
+        <v>478367</v>
       </c>
       <c r="R14" t="n">
-        <v>6950105</v>
+        <v>6950338</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122178286</v>
+        <v>122178275</v>
       </c>
       <c r="B15" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,25 +2079,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478529</v>
+        <v>478318</v>
       </c>
       <c r="R15" t="n">
-        <v>6950164</v>
+        <v>6950174</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122178282</v>
+        <v>122178277</v>
       </c>
       <c r="B16" t="n">
         <v>98196</v>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478489</v>
+        <v>478376</v>
       </c>
       <c r="R16" t="n">
-        <v>6950163</v>
+        <v>6950118</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2271,7 +2271,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122178275</v>
+        <v>122178284</v>
       </c>
       <c r="B17" t="n">
         <v>78645</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478318</v>
+        <v>478499</v>
       </c>
       <c r="R17" t="n">
-        <v>6950174</v>
+        <v>6950188</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122178277</v>
+        <v>122178280</v>
       </c>
       <c r="B18" t="n">
         <v>98196</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478376</v>
+        <v>478460</v>
       </c>
       <c r="R18" t="n">
-        <v>6950118</v>
+        <v>6950137</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122178274</v>
+        <v>122178283</v>
       </c>
       <c r="B19" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2487,25 +2487,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478367</v>
+        <v>478488</v>
       </c>
       <c r="R19" t="n">
-        <v>6950338</v>
+        <v>6950169</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178276</v>
+        <v>122178278</v>
       </c>
       <c r="B20" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,25 +2589,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478356</v>
+        <v>478422</v>
       </c>
       <c r="R20" t="n">
-        <v>6950124</v>
+        <v>6950105</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122178276</v>
+        <v>122178278</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>97139</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,25 +1161,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478356</v>
+        <v>478422</v>
       </c>
       <c r="R6" t="n">
-        <v>6950124</v>
+        <v>6950105</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122178272</v>
+        <v>122178274</v>
       </c>
       <c r="B7" t="n">
-        <v>97129</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,25 +1263,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478246</v>
+        <v>478367</v>
       </c>
       <c r="R7" t="n">
-        <v>6950307</v>
+        <v>6950338</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122178279</v>
+        <v>122178283</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>97139</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,25 +1365,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478454</v>
+        <v>478488</v>
       </c>
       <c r="R8" t="n">
-        <v>6950126</v>
+        <v>6950169</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122178286</v>
+        <v>122178284</v>
       </c>
       <c r="B9" t="n">
-        <v>97129</v>
+        <v>78646</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,25 +1467,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478529</v>
+        <v>478499</v>
       </c>
       <c r="R9" t="n">
-        <v>6950164</v>
+        <v>6950188</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122178273</v>
+        <v>122178280</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>98206</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,25 +1569,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478296</v>
+        <v>478460</v>
       </c>
       <c r="R10" t="n">
-        <v>6950347</v>
+        <v>6950137</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122178285</v>
+        <v>122178286</v>
       </c>
       <c r="B11" t="n">
-        <v>98196</v>
+        <v>97139</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478533</v>
+        <v>478529</v>
       </c>
       <c r="R11" t="n">
-        <v>6950174</v>
+        <v>6950164</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122178282</v>
+        <v>122178285</v>
       </c>
       <c r="B12" t="n">
-        <v>98196</v>
+        <v>98206</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478489</v>
+        <v>478533</v>
       </c>
       <c r="R12" t="n">
-        <v>6950163</v>
+        <v>6950174</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122178281</v>
+        <v>122178282</v>
       </c>
       <c r="B13" t="n">
-        <v>98196</v>
+        <v>98206</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478481</v>
+        <v>478489</v>
       </c>
       <c r="R13" t="n">
-        <v>6950141</v>
+        <v>6950163</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122178274</v>
+        <v>122178277</v>
       </c>
       <c r="B14" t="n">
-        <v>78645</v>
+        <v>98206</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,25 +1977,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478367</v>
+        <v>478376</v>
       </c>
       <c r="R14" t="n">
-        <v>6950338</v>
+        <v>6950118</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122178275</v>
+        <v>122178276</v>
       </c>
       <c r="B15" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478318</v>
+        <v>478356</v>
       </c>
       <c r="R15" t="n">
-        <v>6950174</v>
+        <v>6950124</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122178277</v>
+        <v>122178272</v>
       </c>
       <c r="B16" t="n">
-        <v>98196</v>
+        <v>97139</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478376</v>
+        <v>478246</v>
       </c>
       <c r="R16" t="n">
-        <v>6950118</v>
+        <v>6950307</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122178284</v>
+        <v>122178279</v>
       </c>
       <c r="B17" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478499</v>
+        <v>478454</v>
       </c>
       <c r="R17" t="n">
-        <v>6950188</v>
+        <v>6950126</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2373,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122178280</v>
+        <v>122178275</v>
       </c>
       <c r="B18" t="n">
-        <v>98196</v>
+        <v>78646</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,25 +2385,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478460</v>
+        <v>478318</v>
       </c>
       <c r="R18" t="n">
-        <v>6950137</v>
+        <v>6950174</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122178283</v>
+        <v>122178281</v>
       </c>
       <c r="B19" t="n">
-        <v>97129</v>
+        <v>98206</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,21 +2491,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478488</v>
+        <v>478481</v>
       </c>
       <c r="R19" t="n">
-        <v>6950169</v>
+        <v>6950141</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178278</v>
+        <v>122178273</v>
       </c>
       <c r="B20" t="n">
-        <v>97129</v>
+        <v>78646</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,25 +2589,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478422</v>
+        <v>478296</v>
       </c>
       <c r="R20" t="n">
-        <v>6950105</v>
+        <v>6950347</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122178278</v>
+        <v>122178274</v>
       </c>
       <c r="B6" t="n">
-        <v>97139</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,25 +1161,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478422</v>
+        <v>478367</v>
       </c>
       <c r="R6" t="n">
-        <v>6950105</v>
+        <v>6950338</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122178274</v>
+        <v>122178282</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>98206</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,25 +1263,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478367</v>
+        <v>478489</v>
       </c>
       <c r="R7" t="n">
-        <v>6950338</v>
+        <v>6950163</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122178283</v>
+        <v>122178272</v>
       </c>
       <c r="B8" t="n">
         <v>97139</v>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478488</v>
+        <v>478246</v>
       </c>
       <c r="R8" t="n">
-        <v>6950169</v>
+        <v>6950307</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122178284</v>
+        <v>122178276</v>
       </c>
       <c r="B9" t="n">
         <v>78646</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478499</v>
+        <v>478356</v>
       </c>
       <c r="R9" t="n">
-        <v>6950188</v>
+        <v>6950124</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122178286</v>
+        <v>122178278</v>
       </c>
       <c r="B11" t="n">
         <v>97139</v>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478529</v>
+        <v>478422</v>
       </c>
       <c r="R11" t="n">
-        <v>6950164</v>
+        <v>6950105</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122178282</v>
+        <v>122178283</v>
       </c>
       <c r="B13" t="n">
-        <v>98206</v>
+        <v>97139</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,21 +1879,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478489</v>
+        <v>478488</v>
       </c>
       <c r="R13" t="n">
-        <v>6950163</v>
+        <v>6950169</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122178276</v>
+        <v>122178273</v>
       </c>
       <c r="B15" t="n">
         <v>78646</v>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478356</v>
+        <v>478296</v>
       </c>
       <c r="R15" t="n">
-        <v>6950124</v>
+        <v>6950347</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122178272</v>
+        <v>122178286</v>
       </c>
       <c r="B16" t="n">
         <v>97139</v>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478246</v>
+        <v>478529</v>
       </c>
       <c r="R16" t="n">
-        <v>6950307</v>
+        <v>6950164</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122178279</v>
+        <v>122178281</v>
       </c>
       <c r="B17" t="n">
-        <v>78646</v>
+        <v>98206</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478454</v>
+        <v>478481</v>
       </c>
       <c r="R17" t="n">
-        <v>6950126</v>
+        <v>6950141</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122178281</v>
+        <v>122178284</v>
       </c>
       <c r="B19" t="n">
-        <v>98206</v>
+        <v>78646</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2487,25 +2487,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478481</v>
+        <v>478499</v>
       </c>
       <c r="R19" t="n">
-        <v>6950141</v>
+        <v>6950188</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2577,7 +2577,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178273</v>
+        <v>122178279</v>
       </c>
       <c r="B20" t="n">
         <v>78646</v>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478296</v>
+        <v>478454</v>
       </c>
       <c r="R20" t="n">
-        <v>6950347</v>
+        <v>6950126</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122178274</v>
+        <v>122178282</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>98206</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,25 +1161,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478367</v>
+        <v>478489</v>
       </c>
       <c r="R6" t="n">
-        <v>6950338</v>
+        <v>6950163</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122178282</v>
+        <v>122178274</v>
       </c>
       <c r="B7" t="n">
-        <v>98206</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,25 +1263,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478489</v>
+        <v>478367</v>
       </c>
       <c r="R7" t="n">
-        <v>6950163</v>
+        <v>6950338</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -1152,7 +1152,7 @@
         <v>122178282</v>
       </c>
       <c r="B6" t="n">
-        <v>98206</v>
+        <v>98218</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122178274</v>
+        <v>122178286</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>97151</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,25 +1263,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478367</v>
+        <v>478529</v>
       </c>
       <c r="R7" t="n">
-        <v>6950338</v>
+        <v>6950164</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122178272</v>
+        <v>122178281</v>
       </c>
       <c r="B8" t="n">
-        <v>97139</v>
+        <v>98218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478246</v>
+        <v>478481</v>
       </c>
       <c r="R8" t="n">
-        <v>6950307</v>
+        <v>6950141</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122178276</v>
+        <v>122178284</v>
       </c>
       <c r="B9" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478356</v>
+        <v>478499</v>
       </c>
       <c r="R9" t="n">
-        <v>6950124</v>
+        <v>6950188</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122178280</v>
+        <v>122178276</v>
       </c>
       <c r="B10" t="n">
-        <v>98206</v>
+        <v>78651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,25 +1569,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478460</v>
+        <v>478356</v>
       </c>
       <c r="R10" t="n">
-        <v>6950137</v>
+        <v>6950124</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122178278</v>
+        <v>122178277</v>
       </c>
       <c r="B11" t="n">
-        <v>97139</v>
+        <v>98218</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478422</v>
+        <v>478376</v>
       </c>
       <c r="R11" t="n">
-        <v>6950105</v>
+        <v>6950118</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122178285</v>
+        <v>122178272</v>
       </c>
       <c r="B12" t="n">
-        <v>98206</v>
+        <v>97151</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,21 +1777,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478533</v>
+        <v>478246</v>
       </c>
       <c r="R12" t="n">
-        <v>6950174</v>
+        <v>6950307</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1866,7 +1866,7 @@
         <v>122178283</v>
       </c>
       <c r="B13" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122178277</v>
+        <v>122178280</v>
       </c>
       <c r="B14" t="n">
-        <v>98206</v>
+        <v>98218</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478376</v>
+        <v>478460</v>
       </c>
       <c r="R14" t="n">
-        <v>6950118</v>
+        <v>6950137</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122178273</v>
+        <v>122178275</v>
       </c>
       <c r="B15" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478296</v>
+        <v>478318</v>
       </c>
       <c r="R15" t="n">
-        <v>6950347</v>
+        <v>6950174</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122178286</v>
+        <v>122178285</v>
       </c>
       <c r="B16" t="n">
-        <v>97139</v>
+        <v>98218</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478529</v>
+        <v>478533</v>
       </c>
       <c r="R16" t="n">
-        <v>6950164</v>
+        <v>6950174</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122178281</v>
+        <v>122178278</v>
       </c>
       <c r="B17" t="n">
-        <v>98206</v>
+        <v>97151</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478481</v>
+        <v>478422</v>
       </c>
       <c r="R17" t="n">
-        <v>6950141</v>
+        <v>6950105</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2373,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122178275</v>
+        <v>122178279</v>
       </c>
       <c r="B18" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478318</v>
+        <v>478454</v>
       </c>
       <c r="R18" t="n">
-        <v>6950174</v>
+        <v>6950126</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122178284</v>
+        <v>122178274</v>
       </c>
       <c r="B19" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478499</v>
+        <v>478367</v>
       </c>
       <c r="R19" t="n">
-        <v>6950188</v>
+        <v>6950338</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178279</v>
+        <v>122178273</v>
       </c>
       <c r="B20" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478454</v>
+        <v>478296</v>
       </c>
       <c r="R20" t="n">
-        <v>6950126</v>
+        <v>6950347</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122178282</v>
+        <v>122178286</v>
       </c>
       <c r="B6" t="n">
-        <v>98218</v>
+        <v>97156</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478489</v>
+        <v>478529</v>
       </c>
       <c r="R6" t="n">
-        <v>6950163</v>
+        <v>6950164</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122178286</v>
+        <v>122178280</v>
       </c>
       <c r="B7" t="n">
-        <v>97151</v>
+        <v>98223</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478529</v>
+        <v>478460</v>
       </c>
       <c r="R7" t="n">
-        <v>6950164</v>
+        <v>6950137</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122178281</v>
+        <v>122178278</v>
       </c>
       <c r="B8" t="n">
-        <v>98218</v>
+        <v>97156</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478481</v>
+        <v>478422</v>
       </c>
       <c r="R8" t="n">
-        <v>6950141</v>
+        <v>6950105</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122178284</v>
+        <v>122178276</v>
       </c>
       <c r="B9" t="n">
         <v>78651</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478499</v>
+        <v>478356</v>
       </c>
       <c r="R9" t="n">
-        <v>6950188</v>
+        <v>6950124</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122178276</v>
+        <v>122178272</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>97156</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,25 +1569,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478356</v>
+        <v>478246</v>
       </c>
       <c r="R10" t="n">
-        <v>6950124</v>
+        <v>6950307</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122178277</v>
+        <v>122178275</v>
       </c>
       <c r="B11" t="n">
-        <v>98218</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,25 +1671,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478376</v>
+        <v>478318</v>
       </c>
       <c r="R11" t="n">
-        <v>6950118</v>
+        <v>6950174</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122178272</v>
+        <v>122178282</v>
       </c>
       <c r="B12" t="n">
-        <v>97151</v>
+        <v>98223</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,21 +1777,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478246</v>
+        <v>478489</v>
       </c>
       <c r="R12" t="n">
-        <v>6950307</v>
+        <v>6950163</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122178283</v>
+        <v>122178273</v>
       </c>
       <c r="B13" t="n">
-        <v>97151</v>
+        <v>78651</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,25 +1875,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478488</v>
+        <v>478296</v>
       </c>
       <c r="R13" t="n">
-        <v>6950169</v>
+        <v>6950347</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122178280</v>
+        <v>122178277</v>
       </c>
       <c r="B14" t="n">
-        <v>98218</v>
+        <v>98223</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478460</v>
+        <v>478376</v>
       </c>
       <c r="R14" t="n">
-        <v>6950137</v>
+        <v>6950118</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122178275</v>
+        <v>122178284</v>
       </c>
       <c r="B15" t="n">
         <v>78651</v>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478318</v>
+        <v>478499</v>
       </c>
       <c r="R15" t="n">
-        <v>6950174</v>
+        <v>6950188</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122178285</v>
+        <v>122178283</v>
       </c>
       <c r="B16" t="n">
-        <v>98218</v>
+        <v>97156</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478533</v>
+        <v>478488</v>
       </c>
       <c r="R16" t="n">
-        <v>6950174</v>
+        <v>6950169</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122178278</v>
+        <v>122178279</v>
       </c>
       <c r="B17" t="n">
-        <v>97151</v>
+        <v>78651</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478422</v>
+        <v>478454</v>
       </c>
       <c r="R17" t="n">
-        <v>6950105</v>
+        <v>6950126</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2373,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122178279</v>
+        <v>122178281</v>
       </c>
       <c r="B18" t="n">
-        <v>78651</v>
+        <v>98223</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,25 +2385,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478454</v>
+        <v>478481</v>
       </c>
       <c r="R18" t="n">
-        <v>6950126</v>
+        <v>6950141</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178273</v>
+        <v>122178285</v>
       </c>
       <c r="B20" t="n">
-        <v>78651</v>
+        <v>98223</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,25 +2589,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478296</v>
+        <v>478533</v>
       </c>
       <c r="R20" t="n">
-        <v>6950347</v>
+        <v>6950174</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122178272</v>
+        <v>122178275</v>
       </c>
       <c r="B10" t="n">
-        <v>97156</v>
+        <v>78651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,25 +1569,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478246</v>
+        <v>478318</v>
       </c>
       <c r="R10" t="n">
-        <v>6950307</v>
+        <v>6950174</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122178275</v>
+        <v>122178272</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>97156</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,25 +1671,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478318</v>
+        <v>478246</v>
       </c>
       <c r="R11" t="n">
-        <v>6950174</v>
+        <v>6950307</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122178275</v>
+        <v>122178272</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>97156</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,25 +1569,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478318</v>
+        <v>478246</v>
       </c>
       <c r="R10" t="n">
-        <v>6950174</v>
+        <v>6950307</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122178272</v>
+        <v>122178275</v>
       </c>
       <c r="B11" t="n">
-        <v>97156</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,25 +1671,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478246</v>
+        <v>478318</v>
       </c>
       <c r="R11" t="n">
-        <v>6950307</v>
+        <v>6950174</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122178286</v>
+        <v>122178281</v>
       </c>
       <c r="B6" t="n">
-        <v>97156</v>
+        <v>98232</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,21 +1165,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>221952</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478529</v>
+        <v>478481</v>
       </c>
       <c r="R6" t="n">
-        <v>6950164</v>
+        <v>6950141</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1254,7 +1249,7 @@
         <v>122178280</v>
       </c>
       <c r="B7" t="n">
-        <v>98223</v>
+        <v>98232</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,11 +1263,6 @@
       </c>
       <c r="E7" t="n">
         <v>221952</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1353,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122178278</v>
+        <v>122178284</v>
       </c>
       <c r="B8" t="n">
-        <v>97156</v>
+        <v>78652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,25 +1355,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478422</v>
+        <v>478499</v>
       </c>
       <c r="R8" t="n">
-        <v>6950105</v>
+        <v>6950188</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,7 +1443,7 @@
         <v>122178276</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,11 +1457,6 @@
       </c>
       <c r="E9" t="n">
         <v>6425</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1557,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122178272</v>
+        <v>122178275</v>
       </c>
       <c r="B10" t="n">
-        <v>97156</v>
+        <v>78652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,25 +1549,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478246</v>
+        <v>478318</v>
       </c>
       <c r="R10" t="n">
-        <v>6950307</v>
+        <v>6950174</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122178275</v>
+        <v>122178274</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,11 +1652,6 @@
       <c r="E11" t="n">
         <v>6425</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1699,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478318</v>
+        <v>478367</v>
       </c>
       <c r="R11" t="n">
-        <v>6950174</v>
+        <v>6950338</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1761,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122178282</v>
+        <v>122178273</v>
       </c>
       <c r="B12" t="n">
-        <v>98223</v>
+        <v>78652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,25 +1743,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478489</v>
+        <v>478296</v>
       </c>
       <c r="R12" t="n">
-        <v>6950163</v>
+        <v>6950347</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,10 +1828,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122178273</v>
+        <v>122178272</v>
       </c>
       <c r="B13" t="n">
-        <v>78651</v>
+        <v>97165</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,25 +1840,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1903,10 +1863,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478296</v>
+        <v>478246</v>
       </c>
       <c r="R13" t="n">
-        <v>6950347</v>
+        <v>6950307</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1965,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122178277</v>
+        <v>122178285</v>
       </c>
       <c r="B14" t="n">
-        <v>98223</v>
+        <v>98232</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,11 +1943,6 @@
       <c r="E14" t="n">
         <v>221952</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Neottia cordata</t>
@@ -2005,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478376</v>
+        <v>478533</v>
       </c>
       <c r="R14" t="n">
-        <v>6950118</v>
+        <v>6950174</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2067,10 +2022,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122178284</v>
+        <v>122178277</v>
       </c>
       <c r="B15" t="n">
-        <v>78651</v>
+        <v>98232</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,25 +2034,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>221952</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2107,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478499</v>
+        <v>478376</v>
       </c>
       <c r="R15" t="n">
-        <v>6950188</v>
+        <v>6950118</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122178283</v>
+        <v>122178282</v>
       </c>
       <c r="B16" t="n">
-        <v>97156</v>
+        <v>98232</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2135,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>221952</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2154,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478488</v>
+        <v>478489</v>
       </c>
       <c r="R16" t="n">
-        <v>6950169</v>
+        <v>6950163</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2271,10 +2216,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122178279</v>
+        <v>122178278</v>
       </c>
       <c r="B17" t="n">
-        <v>78651</v>
+        <v>97165</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,25 +2228,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2251,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478454</v>
+        <v>478422</v>
       </c>
       <c r="R17" t="n">
-        <v>6950126</v>
+        <v>6950105</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2373,10 +2313,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122178281</v>
+        <v>122178279</v>
       </c>
       <c r="B18" t="n">
-        <v>98223</v>
+        <v>78652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,25 +2325,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478481</v>
+        <v>478454</v>
       </c>
       <c r="R18" t="n">
-        <v>6950141</v>
+        <v>6950126</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2475,10 +2410,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122178274</v>
+        <v>122178283</v>
       </c>
       <c r="B19" t="n">
-        <v>78651</v>
+        <v>97165</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2487,25 +2422,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2445,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478367</v>
+        <v>478488</v>
       </c>
       <c r="R19" t="n">
-        <v>6950338</v>
+        <v>6950169</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2577,10 +2507,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178285</v>
+        <v>122178286</v>
       </c>
       <c r="B20" t="n">
-        <v>98223</v>
+        <v>97165</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2593,21 +2523,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2617,10 +2542,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478533</v>
+        <v>478529</v>
       </c>
       <c r="R20" t="n">
-        <v>6950174</v>
+        <v>6950164</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122178281</v>
+        <v>122178275</v>
       </c>
       <c r="B6" t="n">
-        <v>98232</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,20 +1161,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478481</v>
+        <v>478318</v>
       </c>
       <c r="R6" t="n">
-        <v>6950141</v>
+        <v>6950174</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1246,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122178280</v>
+        <v>122178278</v>
       </c>
       <c r="B7" t="n">
-        <v>98232</v>
+        <v>97178</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,16 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478460</v>
+        <v>478422</v>
       </c>
       <c r="R7" t="n">
-        <v>6950137</v>
+        <v>6950105</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122178284</v>
+        <v>122178279</v>
       </c>
       <c r="B8" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,6 +1371,11 @@
       <c r="E8" t="n">
         <v>6425</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1378,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478499</v>
+        <v>478454</v>
       </c>
       <c r="R8" t="n">
-        <v>6950188</v>
+        <v>6950126</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122178276</v>
+        <v>122178280</v>
       </c>
       <c r="B9" t="n">
-        <v>78652</v>
+        <v>98245</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,20 +1467,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478356</v>
+        <v>478460</v>
       </c>
       <c r="R9" t="n">
-        <v>6950124</v>
+        <v>6950137</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1537,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122178275</v>
+        <v>122178285</v>
       </c>
       <c r="B10" t="n">
-        <v>78652</v>
+        <v>98245</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,20 +1569,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1572,7 +1597,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478318</v>
+        <v>478533</v>
       </c>
       <c r="R10" t="n">
         <v>6950174</v>
@@ -1634,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122178274</v>
+        <v>122178281</v>
       </c>
       <c r="B11" t="n">
-        <v>78652</v>
+        <v>98245</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,20 +1671,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221952</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478367</v>
+        <v>478481</v>
       </c>
       <c r="R11" t="n">
-        <v>6950338</v>
+        <v>6950141</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1734,7 +1764,7 @@
         <v>122178273</v>
       </c>
       <c r="B12" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,6 +1778,11 @@
       </c>
       <c r="E12" t="n">
         <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1828,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122178272</v>
+        <v>122178282</v>
       </c>
       <c r="B13" t="n">
-        <v>97165</v>
+        <v>98245</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,16 +1879,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>221952</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1863,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478246</v>
+        <v>478489</v>
       </c>
       <c r="R13" t="n">
-        <v>6950307</v>
+        <v>6950163</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1925,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122178285</v>
+        <v>122178274</v>
       </c>
       <c r="B14" t="n">
-        <v>98232</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1937,20 +1977,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1960,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478533</v>
+        <v>478367</v>
       </c>
       <c r="R14" t="n">
-        <v>6950174</v>
+        <v>6950338</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2025,7 +2070,7 @@
         <v>122178277</v>
       </c>
       <c r="B15" t="n">
-        <v>98232</v>
+        <v>98245</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2039,6 +2084,11 @@
       </c>
       <c r="E15" t="n">
         <v>221952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2119,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122178282</v>
+        <v>122178286</v>
       </c>
       <c r="B16" t="n">
-        <v>98232</v>
+        <v>97178</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,16 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2154,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478489</v>
+        <v>478529</v>
       </c>
       <c r="R16" t="n">
-        <v>6950163</v>
+        <v>6950164</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2216,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122178278</v>
+        <v>122178272</v>
       </c>
       <c r="B17" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2234,6 +2289,11 @@
       <c r="E17" t="n">
         <v>221945</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -2251,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478422</v>
+        <v>478246</v>
       </c>
       <c r="R17" t="n">
-        <v>6950105</v>
+        <v>6950307</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2313,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122178279</v>
+        <v>122178284</v>
       </c>
       <c r="B18" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2331,6 +2391,11 @@
       <c r="E18" t="n">
         <v>6425</v>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2348,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478454</v>
+        <v>478499</v>
       </c>
       <c r="R18" t="n">
-        <v>6950126</v>
+        <v>6950188</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2413,7 +2478,7 @@
         <v>122178283</v>
       </c>
       <c r="B19" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2427,6 +2492,11 @@
       </c>
       <c r="E19" t="n">
         <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2507,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178286</v>
+        <v>122178276</v>
       </c>
       <c r="B20" t="n">
-        <v>97165</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2519,20 +2589,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2542,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478529</v>
+        <v>478356</v>
       </c>
       <c r="R20" t="n">
-        <v>6950164</v>
+        <v>6950124</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122178275</v>
+        <v>122178283</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,25 +1161,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478318</v>
+        <v>478488</v>
       </c>
       <c r="R6" t="n">
-        <v>6950174</v>
+        <v>6950169</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1254,7 +1254,7 @@
         <v>122178278</v>
       </c>
       <c r="B7" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122178279</v>
+        <v>122178274</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478454</v>
+        <v>478367</v>
       </c>
       <c r="R8" t="n">
-        <v>6950126</v>
+        <v>6950338</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,7 +1458,7 @@
         <v>122178280</v>
       </c>
       <c r="B9" t="n">
-        <v>98245</v>
+        <v>98258</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122178285</v>
+        <v>122178281</v>
       </c>
       <c r="B10" t="n">
-        <v>98245</v>
+        <v>98258</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478533</v>
+        <v>478481</v>
       </c>
       <c r="R10" t="n">
-        <v>6950174</v>
+        <v>6950141</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122178281</v>
+        <v>122178277</v>
       </c>
       <c r="B11" t="n">
-        <v>98245</v>
+        <v>98258</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478481</v>
+        <v>478376</v>
       </c>
       <c r="R11" t="n">
-        <v>6950141</v>
+        <v>6950118</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122178273</v>
+        <v>122178286</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,25 +1773,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478296</v>
+        <v>478529</v>
       </c>
       <c r="R12" t="n">
-        <v>6950347</v>
+        <v>6950164</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1866,7 +1866,7 @@
         <v>122178282</v>
       </c>
       <c r="B13" t="n">
-        <v>98245</v>
+        <v>98258</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122178274</v>
+        <v>122178273</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478367</v>
+        <v>478296</v>
       </c>
       <c r="R14" t="n">
-        <v>6950338</v>
+        <v>6950347</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122178277</v>
+        <v>122178279</v>
       </c>
       <c r="B15" t="n">
-        <v>98245</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,25 +2079,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478376</v>
+        <v>478454</v>
       </c>
       <c r="R15" t="n">
-        <v>6950118</v>
+        <v>6950126</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122178286</v>
+        <v>122178276</v>
       </c>
       <c r="B16" t="n">
-        <v>97178</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478529</v>
+        <v>478356</v>
       </c>
       <c r="R16" t="n">
-        <v>6950164</v>
+        <v>6950124</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122178272</v>
+        <v>122178285</v>
       </c>
       <c r="B17" t="n">
-        <v>97178</v>
+        <v>98258</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,21 +2287,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478246</v>
+        <v>478533</v>
       </c>
       <c r="R17" t="n">
-        <v>6950307</v>
+        <v>6950174</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122178284</v>
+        <v>122178275</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478499</v>
+        <v>478318</v>
       </c>
       <c r="R18" t="n">
-        <v>6950188</v>
+        <v>6950174</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122178283</v>
+        <v>122178284</v>
       </c>
       <c r="B19" t="n">
-        <v>97178</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2487,25 +2487,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478488</v>
+        <v>478499</v>
       </c>
       <c r="R19" t="n">
-        <v>6950169</v>
+        <v>6950188</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178276</v>
+        <v>122178272</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,25 +2589,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478356</v>
+        <v>478246</v>
       </c>
       <c r="R20" t="n">
-        <v>6950124</v>
+        <v>6950307</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122178283</v>
+        <v>122178282</v>
       </c>
       <c r="B6" t="n">
-        <v>97191</v>
+        <v>98258</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478488</v>
+        <v>478489</v>
       </c>
       <c r="R6" t="n">
-        <v>6950169</v>
+        <v>6950163</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122178278</v>
+        <v>122178281</v>
       </c>
       <c r="B7" t="n">
-        <v>97191</v>
+        <v>98258</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478422</v>
+        <v>478481</v>
       </c>
       <c r="R7" t="n">
-        <v>6950105</v>
+        <v>6950141</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122178274</v>
+        <v>122178275</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478367</v>
+        <v>478318</v>
       </c>
       <c r="R8" t="n">
-        <v>6950338</v>
+        <v>6950174</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122178280</v>
+        <v>122178274</v>
       </c>
       <c r="B9" t="n">
-        <v>98258</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,25 +1467,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478460</v>
+        <v>478367</v>
       </c>
       <c r="R9" t="n">
-        <v>6950137</v>
+        <v>6950338</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122178281</v>
+        <v>122178280</v>
       </c>
       <c r="B10" t="n">
         <v>98258</v>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478481</v>
+        <v>478460</v>
       </c>
       <c r="R10" t="n">
-        <v>6950141</v>
+        <v>6950137</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122178277</v>
+        <v>122178283</v>
       </c>
       <c r="B11" t="n">
-        <v>98258</v>
+        <v>97191</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478376</v>
+        <v>478488</v>
       </c>
       <c r="R11" t="n">
-        <v>6950118</v>
+        <v>6950169</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122178286</v>
+        <v>122178276</v>
       </c>
       <c r="B12" t="n">
-        <v>97191</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,25 +1773,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478529</v>
+        <v>478356</v>
       </c>
       <c r="R12" t="n">
-        <v>6950164</v>
+        <v>6950124</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,7 +1863,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122178282</v>
+        <v>122178285</v>
       </c>
       <c r="B13" t="n">
         <v>98258</v>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478489</v>
+        <v>478533</v>
       </c>
       <c r="R13" t="n">
-        <v>6950163</v>
+        <v>6950174</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122178273</v>
+        <v>122178284</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478296</v>
+        <v>478499</v>
       </c>
       <c r="R14" t="n">
-        <v>6950347</v>
+        <v>6950188</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122178279</v>
+        <v>122178286</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,25 +2079,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478454</v>
+        <v>478529</v>
       </c>
       <c r="R15" t="n">
-        <v>6950126</v>
+        <v>6950164</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122178276</v>
+        <v>122178279</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478356</v>
+        <v>478454</v>
       </c>
       <c r="R16" t="n">
-        <v>6950124</v>
+        <v>6950126</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122178285</v>
+        <v>122178273</v>
       </c>
       <c r="B17" t="n">
-        <v>98258</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478533</v>
+        <v>478296</v>
       </c>
       <c r="R17" t="n">
-        <v>6950174</v>
+        <v>6950347</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2373,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122178275</v>
+        <v>122178277</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>98258</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,25 +2385,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478318</v>
+        <v>478376</v>
       </c>
       <c r="R18" t="n">
-        <v>6950174</v>
+        <v>6950118</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122178284</v>
+        <v>122178278</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2487,25 +2487,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478499</v>
+        <v>478422</v>
       </c>
       <c r="R19" t="n">
-        <v>6950188</v>
+        <v>6950105</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2677,6 +2677,228 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125657691</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57738</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>478330</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6950126</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125657692</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56828</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>478330</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6950128</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125800103</v>
+        <v>125798806</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>91220</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,21 +2902,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478279</v>
+        <v>478289</v>
       </c>
       <c r="R23" t="n">
-        <v>6950281</v>
+        <v>6950427</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2959,24 +2959,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2991,22 +2976,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125798806</v>
+        <v>125800103</v>
       </c>
       <c r="B24" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,21 +2999,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3038,13 +3023,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478289</v>
+        <v>478279</v>
       </c>
       <c r="R24" t="n">
-        <v>6950427</v>
+        <v>6950281</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3071,9 +3056,24 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3088,12 +3088,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -5597,10 +5597,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125807838</v>
+        <v>125802867</v>
       </c>
       <c r="B49" t="n">
-        <v>79046</v>
+        <v>78967</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5608,37 +5608,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478276</v>
+        <v>478281</v>
       </c>
       <c r="R49" t="n">
-        <v>6950250</v>
+        <v>6950219</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5665,9 +5665,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5682,22 +5692,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125802867</v>
+        <v>125807838</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>79046</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5705,37 +5715,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478281</v>
+        <v>478276</v>
       </c>
       <c r="R50" t="n">
-        <v>6950219</v>
+        <v>6950250</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5762,19 +5772,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5789,12 +5789,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125798806</v>
+        <v>125800103</v>
       </c>
       <c r="B23" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,21 +2902,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478289</v>
+        <v>478279</v>
       </c>
       <c r="R23" t="n">
-        <v>6950427</v>
+        <v>6950281</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2959,9 +2959,24 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,22 +2991,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125800103</v>
+        <v>125798806</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,21 +3014,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3023,13 +3038,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478279</v>
+        <v>478289</v>
       </c>
       <c r="R24" t="n">
-        <v>6950281</v>
+        <v>6950427</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3056,24 +3071,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3088,12 +3088,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125802853</v>
+        <v>125807839</v>
       </c>
       <c r="B26" t="n">
-        <v>78373</v>
+        <v>78634</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,37 +3208,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478364</v>
+        <v>478450</v>
       </c>
       <c r="R26" t="n">
-        <v>6950434</v>
+        <v>6950228</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3265,19 +3265,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3292,22 +3282,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125807839</v>
+        <v>125802853</v>
       </c>
       <c r="B27" t="n">
-        <v>78634</v>
+        <v>78373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3315,37 +3305,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478450</v>
+        <v>478364</v>
       </c>
       <c r="R27" t="n">
-        <v>6950228</v>
+        <v>6950434</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3372,9 +3362,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3389,12 +3389,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3510,7 +3510,7 @@
         <v>125799925</v>
       </c>
       <c r="B29" t="n">
-        <v>91671</v>
+        <v>91678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3614,48 +3614,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125802884</v>
+        <v>125799882</v>
       </c>
       <c r="B30" t="n">
-        <v>98345</v>
+        <v>91227</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478449</v>
+        <v>478301</v>
       </c>
       <c r="R30" t="n">
-        <v>6950182</v>
+        <v>6950180</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3709,60 +3709,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125799882</v>
+        <v>125802884</v>
       </c>
       <c r="B31" t="n">
-        <v>91220</v>
+        <v>98352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478301</v>
+        <v>478449</v>
       </c>
       <c r="R31" t="n">
-        <v>6950180</v>
+        <v>6950182</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3816,44 +3816,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125802866</v>
+        <v>125802868</v>
       </c>
       <c r="B32" t="n">
-        <v>91513</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478281</v>
+        <v>478280</v>
       </c>
       <c r="R32" t="n">
-        <v>6950219</v>
+        <v>6950190</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3935,48 +3935,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125802868</v>
+        <v>125799436</v>
       </c>
       <c r="B33" t="n">
-        <v>98345</v>
+        <v>91678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478280</v>
+        <v>478281</v>
       </c>
       <c r="R33" t="n">
-        <v>6950190</v>
+        <v>6950242</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4003,19 +4003,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4030,60 +4020,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125799436</v>
+        <v>125802866</v>
       </c>
       <c r="B34" t="n">
-        <v>91671</v>
+        <v>91520</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
         <v>478281</v>
       </c>
       <c r="R34" t="n">
-        <v>6950242</v>
+        <v>6950219</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4110,9 +4100,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4127,12 +4127,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4450,32 +4450,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125799113</v>
+        <v>125799913</v>
       </c>
       <c r="B38" t="n">
-        <v>91513</v>
+        <v>91192</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478286</v>
+        <v>478328</v>
       </c>
       <c r="R38" t="n">
-        <v>6950325</v>
+        <v>6950173</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4547,32 +4547,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125799913</v>
+        <v>125799113</v>
       </c>
       <c r="B39" t="n">
-        <v>91185</v>
+        <v>91520</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478328</v>
+        <v>478286</v>
       </c>
       <c r="R39" t="n">
-        <v>6950173</v>
+        <v>6950325</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4754,7 +4754,7 @@
         <v>125800087</v>
       </c>
       <c r="B41" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125802862</v>
+        <v>125802878</v>
       </c>
       <c r="B43" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478280</v>
+        <v>478404</v>
       </c>
       <c r="R43" t="n">
-        <v>6950247</v>
+        <v>6950178</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5062,10 +5062,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125802863</v>
+        <v>125802862</v>
       </c>
       <c r="B44" t="n">
-        <v>91220</v>
+        <v>91520</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478273</v>
+        <v>478280</v>
       </c>
       <c r="R44" t="n">
-        <v>6950245</v>
+        <v>6950247</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802883</v>
+        <v>125802863</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>91227</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478412</v>
+        <v>478273</v>
       </c>
       <c r="R45" t="n">
-        <v>6950164</v>
+        <v>6950245</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125797150</v>
+        <v>125802883</v>
       </c>
       <c r="B46" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,42 +5287,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478393</v>
+        <v>478412</v>
       </c>
       <c r="R46" t="n">
-        <v>6950404</v>
+        <v>6950164</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5349,14 +5344,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5371,60 +5371,65 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802877</v>
+        <v>125797150</v>
       </c>
       <c r="B47" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478396</v>
+        <v>478393</v>
       </c>
       <c r="R47" t="n">
-        <v>6950183</v>
+        <v>6950404</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5451,19 +5456,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5478,44 +5478,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125802878</v>
+        <v>125802877</v>
       </c>
       <c r="B48" t="n">
-        <v>91513</v>
+        <v>98352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478404</v>
+        <v>478396</v>
       </c>
       <c r="R48" t="n">
-        <v>6950178</v>
+        <v>6950183</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5597,10 +5597,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125802867</v>
+        <v>125807838</v>
       </c>
       <c r="B49" t="n">
-        <v>78967</v>
+        <v>79046</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5608,37 +5608,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478281</v>
+        <v>478276</v>
       </c>
       <c r="R49" t="n">
-        <v>6950219</v>
+        <v>6950250</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5665,19 +5665,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5692,22 +5682,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125807838</v>
+        <v>125802867</v>
       </c>
       <c r="B50" t="n">
-        <v>79046</v>
+        <v>78967</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5715,37 +5705,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478276</v>
+        <v>478281</v>
       </c>
       <c r="R50" t="n">
-        <v>6950250</v>
+        <v>6950219</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5772,9 +5762,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5789,57 +5789,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125800061</v>
+        <v>125802870</v>
       </c>
       <c r="B51" t="n">
-        <v>91513</v>
+        <v>98352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478319</v>
+        <v>478330</v>
       </c>
       <c r="R51" t="n">
-        <v>6950199</v>
+        <v>6950181</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5869,9 +5869,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5886,22 +5896,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125799056</v>
+        <v>125800061</v>
       </c>
       <c r="B52" t="n">
-        <v>91220</v>
+        <v>91520</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5909,21 +5919,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5933,10 +5943,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478298</v>
+        <v>478319</v>
       </c>
       <c r="R52" t="n">
-        <v>6950374</v>
+        <v>6950199</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5995,32 +6005,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125802870</v>
+        <v>125802855</v>
       </c>
       <c r="B53" t="n">
-        <v>98345</v>
+        <v>78373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6030,13 +6040,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478330</v>
+        <v>478311</v>
       </c>
       <c r="R53" t="n">
-        <v>6950181</v>
+        <v>6950419</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6065,7 +6075,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6075,7 +6085,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6102,7 +6112,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125802855</v>
+        <v>125807840</v>
       </c>
       <c r="B54" t="n">
         <v>78373</v>
@@ -6133,17 +6143,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478311</v>
+        <v>478314</v>
       </c>
       <c r="R54" t="n">
-        <v>6950419</v>
+        <v>6950423</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6170,19 +6180,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6197,22 +6197,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125807840</v>
+        <v>125799056</v>
       </c>
       <c r="B55" t="n">
-        <v>78373</v>
+        <v>91227</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6220,34 +6220,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478314</v>
+        <v>478298</v>
       </c>
       <c r="R55" t="n">
-        <v>6950423</v>
+        <v>6950374</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6294,12 +6294,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6309,7 +6309,7 @@
         <v>125800829</v>
       </c>
       <c r="B56" t="n">
-        <v>91577</v>
+        <v>91584</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>125799789</v>
       </c>
       <c r="B57" t="n">
-        <v>91234</v>
+        <v>91241</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>125795897</v>
       </c>
       <c r="B58" t="n">
-        <v>91671</v>
+        <v>91678</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>125807837</v>
       </c>
       <c r="B60" t="n">
-        <v>91914</v>
+        <v>91921</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>125833009</v>
       </c>
       <c r="B64" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>125833008</v>
       </c>
       <c r="B66" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>125833006</v>
       </c>
       <c r="B68" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>125833018</v>
       </c>
       <c r="B69" t="n">
-        <v>91671</v>
+        <v>91678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>125833007</v>
       </c>
       <c r="B70" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>125799318</v>
       </c>
       <c r="B72" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -3935,48 +3935,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125799436</v>
+        <v>125802866</v>
       </c>
       <c r="B33" t="n">
-        <v>91678</v>
+        <v>91520</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
         <v>478281</v>
       </c>
       <c r="R33" t="n">
-        <v>6950242</v>
+        <v>6950219</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4003,9 +4003,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4020,60 +4030,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125802866</v>
+        <v>125799436</v>
       </c>
       <c r="B34" t="n">
-        <v>91520</v>
+        <v>91678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
         <v>478281</v>
       </c>
       <c r="R34" t="n">
-        <v>6950219</v>
+        <v>6950242</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4100,19 +4110,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4127,12 +4127,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4353,45 +4353,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125807835</v>
+        <v>125799913</v>
       </c>
       <c r="B37" t="n">
-        <v>79556</v>
+        <v>91192</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478334</v>
+        <v>478328</v>
       </c>
       <c r="R37" t="n">
-        <v>6950420</v>
+        <v>6950173</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4438,44 +4438,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125799913</v>
+        <v>125799113</v>
       </c>
       <c r="B38" t="n">
-        <v>91192</v>
+        <v>91520</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478328</v>
+        <v>478286</v>
       </c>
       <c r="R38" t="n">
-        <v>6950173</v>
+        <v>6950325</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4547,10 +4547,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125799113</v>
+        <v>125807835</v>
       </c>
       <c r="B39" t="n">
-        <v>91520</v>
+        <v>79556</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4558,34 +4558,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478286</v>
+        <v>478334</v>
       </c>
       <c r="R39" t="n">
-        <v>6950325</v>
+        <v>6950420</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4632,12 +4632,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -3006,7 +3006,7 @@
         <v>125798806</v>
       </c>
       <c r="B24" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>125800701</v>
       </c>
       <c r="B25" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>125807839</v>
       </c>
       <c r="B26" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>125802853</v>
       </c>
       <c r="B27" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,52 +3401,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125808994</v>
+        <v>125799925</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>91679</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Klippberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478416</v>
+        <v>478282</v>
       </c>
       <c r="R28" t="n">
-        <v>6950415</v>
+        <v>6950251</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3473,14 +3469,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3495,60 +3496,64 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125799925</v>
+        <v>125808994</v>
       </c>
       <c r="B29" t="n">
-        <v>91678</v>
+        <v>57651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Klippberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478282</v>
+        <v>478416</v>
       </c>
       <c r="R29" t="n">
-        <v>6950251</v>
+        <v>6950415</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3575,19 +3580,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:04</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3602,12 +3602,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3617,7 +3617,7 @@
         <v>125799882</v>
       </c>
       <c r="B30" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>125802884</v>
       </c>
       <c r="B31" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>125802868</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3935,48 +3935,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125802866</v>
+        <v>125799436</v>
       </c>
       <c r="B33" t="n">
-        <v>91520</v>
+        <v>91679</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
         <v>478281</v>
       </c>
       <c r="R33" t="n">
-        <v>6950219</v>
+        <v>6950242</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4003,19 +4003,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4030,60 +4020,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125799436</v>
+        <v>125802866</v>
       </c>
       <c r="B34" t="n">
-        <v>91678</v>
+        <v>91521</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
         <v>478281</v>
       </c>
       <c r="R34" t="n">
-        <v>6950242</v>
+        <v>6950219</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4110,9 +4100,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4127,12 +4127,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4142,7 +4142,7 @@
         <v>125802861</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>125802887</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4353,32 +4353,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125799913</v>
+        <v>125799113</v>
       </c>
       <c r="B37" t="n">
-        <v>91192</v>
+        <v>91521</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478328</v>
+        <v>478286</v>
       </c>
       <c r="R37" t="n">
-        <v>6950173</v>
+        <v>6950325</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4450,32 +4450,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125799113</v>
+        <v>125799913</v>
       </c>
       <c r="B38" t="n">
-        <v>91520</v>
+        <v>91193</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478286</v>
+        <v>478328</v>
       </c>
       <c r="R38" t="n">
-        <v>6950325</v>
+        <v>6950173</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4550,7 +4550,7 @@
         <v>125807835</v>
       </c>
       <c r="B39" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>125802871</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>125800087</v>
       </c>
       <c r="B41" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>125802854</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125802878</v>
+        <v>125797150</v>
       </c>
       <c r="B43" t="n">
-        <v>91520</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4966,37 +4966,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478404</v>
+        <v>478393</v>
       </c>
       <c r="R43" t="n">
-        <v>6950178</v>
+        <v>6950404</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5023,19 +5028,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:15</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5050,22 +5050,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125802862</v>
+        <v>125802883</v>
       </c>
       <c r="B44" t="n">
-        <v>91520</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478280</v>
+        <v>478412</v>
       </c>
       <c r="R44" t="n">
-        <v>6950247</v>
+        <v>6950164</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802863</v>
+        <v>125802878</v>
       </c>
       <c r="B45" t="n">
-        <v>91227</v>
+        <v>91521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478273</v>
+        <v>478404</v>
       </c>
       <c r="R45" t="n">
-        <v>6950245</v>
+        <v>6950178</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125802883</v>
+        <v>125802862</v>
       </c>
       <c r="B46" t="n">
-        <v>78967</v>
+        <v>91521</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478412</v>
+        <v>478280</v>
       </c>
       <c r="R46" t="n">
-        <v>6950164</v>
+        <v>6950247</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125797150</v>
+        <v>125802863</v>
       </c>
       <c r="B47" t="n">
-        <v>57651</v>
+        <v>91228</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,42 +5394,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478393</v>
+        <v>478273</v>
       </c>
       <c r="R47" t="n">
-        <v>6950404</v>
+        <v>6950245</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5456,14 +5451,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5478,12 +5478,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5493,7 +5493,7 @@
         <v>125802877</v>
       </c>
       <c r="B48" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>125807838</v>
       </c>
       <c r="B49" t="n">
-        <v>79046</v>
+        <v>79047</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>125802867</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,45 +5801,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802870</v>
+        <v>125799056</v>
       </c>
       <c r="B51" t="n">
-        <v>98352</v>
+        <v>91228</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478330</v>
+        <v>478298</v>
       </c>
       <c r="R51" t="n">
-        <v>6950181</v>
+        <v>6950374</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5869,19 +5869,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5896,22 +5886,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125800061</v>
+        <v>125802855</v>
       </c>
       <c r="B52" t="n">
-        <v>91520</v>
+        <v>78374</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5919,37 +5909,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478319</v>
+        <v>478311</v>
       </c>
       <c r="R52" t="n">
-        <v>6950199</v>
+        <v>6950419</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5976,9 +5966,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5993,22 +5993,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125802855</v>
+        <v>125807840</v>
       </c>
       <c r="B53" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6036,17 +6036,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478311</v>
+        <v>478314</v>
       </c>
       <c r="R53" t="n">
-        <v>6950419</v>
+        <v>6950423</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6073,19 +6073,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6100,22 +6090,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125807840</v>
+        <v>125800061</v>
       </c>
       <c r="B54" t="n">
-        <v>78373</v>
+        <v>91521</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6123,34 +6113,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478314</v>
+        <v>478319</v>
       </c>
       <c r="R54" t="n">
-        <v>6950423</v>
+        <v>6950199</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6197,57 +6187,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125799056</v>
+        <v>125802870</v>
       </c>
       <c r="B55" t="n">
-        <v>91227</v>
+        <v>98353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478298</v>
+        <v>478330</v>
       </c>
       <c r="R55" t="n">
-        <v>6950374</v>
+        <v>6950181</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6277,9 +6267,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6294,44 +6294,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125800829</v>
+        <v>125799789</v>
       </c>
       <c r="B56" t="n">
-        <v>91584</v>
+        <v>91242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2063</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478489</v>
+        <v>478279</v>
       </c>
       <c r="R56" t="n">
-        <v>6950236</v>
+        <v>6950281</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6374,9 +6374,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6391,44 +6401,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125799789</v>
+        <v>125795897</v>
       </c>
       <c r="B57" t="n">
-        <v>91241</v>
+        <v>91679</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6438,13 +6448,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478279</v>
+        <v>478293</v>
       </c>
       <c r="R57" t="n">
-        <v>6950281</v>
+        <v>6950485</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6471,19 +6481,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6498,22 +6498,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125795897</v>
+        <v>125800829</v>
       </c>
       <c r="B58" t="n">
-        <v>91678</v>
+        <v>91585</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>2063</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478293</v>
+        <v>478489</v>
       </c>
       <c r="R58" t="n">
-        <v>6950485</v>
+        <v>6950236</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6610,7 +6610,7 @@
         <v>125802858</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6714,48 +6714,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125807837</v>
+        <v>125802875</v>
       </c>
       <c r="B60" t="n">
-        <v>91921</v>
+        <v>78968</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478281</v>
+        <v>478367</v>
       </c>
       <c r="R60" t="n">
-        <v>6950244</v>
+        <v>6950197</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6782,9 +6782,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6799,60 +6809,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125802875</v>
+        <v>125807837</v>
       </c>
       <c r="B61" t="n">
-        <v>78967</v>
+        <v>91922</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478367</v>
+        <v>478281</v>
       </c>
       <c r="R61" t="n">
-        <v>6950197</v>
+        <v>6950244</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6879,19 +6889,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6906,12 +6906,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6921,7 +6921,7 @@
         <v>125802859</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>125797369</v>
       </c>
       <c r="B63" t="n">
-        <v>78991</v>
+        <v>78992</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>125833009</v>
       </c>
       <c r="B64" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>125833008</v>
       </c>
       <c r="B66" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>125833006</v>
       </c>
       <c r="B68" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>125833018</v>
       </c>
       <c r="B69" t="n">
-        <v>91678</v>
+        <v>91679</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>125833007</v>
       </c>
       <c r="B70" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>125799318</v>
       </c>
       <c r="B72" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -3401,48 +3401,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125799925</v>
+        <v>125808994</v>
       </c>
       <c r="B28" t="n">
-        <v>91679</v>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Klippberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478282</v>
+        <v>478416</v>
       </c>
       <c r="R28" t="n">
-        <v>6950251</v>
+        <v>6950415</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3469,19 +3473,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:04</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3496,64 +3495,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125808994</v>
+        <v>125799925</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>91682</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Klippberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478416</v>
+        <v>478282</v>
       </c>
       <c r="R29" t="n">
-        <v>6950415</v>
+        <v>6950251</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3580,14 +3575,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3602,60 +3602,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125799882</v>
+        <v>125802884</v>
       </c>
       <c r="B30" t="n">
-        <v>91228</v>
+        <v>98355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478301</v>
+        <v>478449</v>
       </c>
       <c r="R30" t="n">
-        <v>6950180</v>
+        <v>6950182</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3709,60 +3709,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125802884</v>
+        <v>125799882</v>
       </c>
       <c r="B31" t="n">
-        <v>98353</v>
+        <v>91228</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478449</v>
+        <v>478301</v>
       </c>
       <c r="R31" t="n">
-        <v>6950182</v>
+        <v>6950180</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3816,12 +3816,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
         <v>125802868</v>
       </c>
       <c r="B32" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>125799436</v>
       </c>
       <c r="B33" t="n">
-        <v>91679</v>
+        <v>91682</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>125802866</v>
       </c>
       <c r="B34" t="n">
-        <v>91521</v>
+        <v>91524</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125799113</v>
+        <v>125807835</v>
       </c>
       <c r="B37" t="n">
-        <v>91521</v>
+        <v>79557</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4364,34 +4364,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478286</v>
+        <v>478334</v>
       </c>
       <c r="R37" t="n">
-        <v>6950325</v>
+        <v>6950420</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4438,12 +4438,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4547,10 +4547,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125807835</v>
+        <v>125799113</v>
       </c>
       <c r="B39" t="n">
-        <v>79557</v>
+        <v>91524</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4558,34 +4558,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478334</v>
+        <v>478286</v>
       </c>
       <c r="R39" t="n">
-        <v>6950420</v>
+        <v>6950325</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4632,12 +4632,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125800087</v>
+        <v>125802854</v>
       </c>
       <c r="B41" t="n">
-        <v>91228</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478329</v>
+        <v>478350</v>
       </c>
       <c r="R41" t="n">
-        <v>6950196</v>
+        <v>6950427</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,9 +4819,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4836,22 +4846,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125802854</v>
+        <v>125800087</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>91228</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4859,37 +4869,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478350</v>
+        <v>478329</v>
       </c>
       <c r="R42" t="n">
-        <v>6950427</v>
+        <v>6950196</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4916,19 +4926,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,22 +4943,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125797150</v>
+        <v>125802878</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>91524</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4966,42 +4966,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478393</v>
+        <v>478404</v>
       </c>
       <c r="R43" t="n">
-        <v>6950404</v>
+        <v>6950178</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5028,14 +5023,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5050,22 +5050,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125802883</v>
+        <v>125802862</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>91524</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478412</v>
+        <v>478280</v>
       </c>
       <c r="R44" t="n">
-        <v>6950164</v>
+        <v>6950247</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802878</v>
+        <v>125802863</v>
       </c>
       <c r="B45" t="n">
-        <v>91521</v>
+        <v>91228</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478404</v>
+        <v>478273</v>
       </c>
       <c r="R45" t="n">
-        <v>6950178</v>
+        <v>6950245</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125802862</v>
+        <v>125797150</v>
       </c>
       <c r="B46" t="n">
-        <v>91521</v>
+        <v>57651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,37 +5287,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478280</v>
+        <v>478393</v>
       </c>
       <c r="R46" t="n">
-        <v>6950247</v>
+        <v>6950404</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5344,19 +5349,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:50</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5371,22 +5371,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802863</v>
+        <v>125802883</v>
       </c>
       <c r="B47" t="n">
-        <v>91228</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478273</v>
+        <v>478412</v>
       </c>
       <c r="R47" t="n">
-        <v>6950245</v>
+        <v>6950164</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5493,7 +5493,7 @@
         <v>125802877</v>
       </c>
       <c r="B48" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5801,45 +5801,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125799056</v>
+        <v>125802870</v>
       </c>
       <c r="B51" t="n">
-        <v>91228</v>
+        <v>98355</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478298</v>
+        <v>478330</v>
       </c>
       <c r="R51" t="n">
-        <v>6950374</v>
+        <v>6950181</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5869,9 +5869,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5886,22 +5896,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802855</v>
+        <v>125800061</v>
       </c>
       <c r="B52" t="n">
-        <v>78374</v>
+        <v>91524</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5909,37 +5919,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478311</v>
+        <v>478319</v>
       </c>
       <c r="R52" t="n">
-        <v>6950419</v>
+        <v>6950199</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5966,19 +5976,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5993,19 +5993,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125807840</v>
+        <v>125802855</v>
       </c>
       <c r="B53" t="n">
         <v>78374</v>
@@ -6036,17 +6036,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478314</v>
+        <v>478311</v>
       </c>
       <c r="R53" t="n">
-        <v>6950423</v>
+        <v>6950419</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6073,9 +6073,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6090,22 +6100,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125800061</v>
+        <v>125807840</v>
       </c>
       <c r="B54" t="n">
-        <v>91521</v>
+        <v>78374</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6113,34 +6123,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478319</v>
+        <v>478314</v>
       </c>
       <c r="R54" t="n">
-        <v>6950199</v>
+        <v>6950423</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6187,57 +6197,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125802870</v>
+        <v>125799056</v>
       </c>
       <c r="B55" t="n">
-        <v>98353</v>
+        <v>91228</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478330</v>
+        <v>478298</v>
       </c>
       <c r="R55" t="n">
-        <v>6950181</v>
+        <v>6950374</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6267,19 +6277,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6294,12 +6294,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6416,7 +6416,7 @@
         <v>125795897</v>
       </c>
       <c r="B57" t="n">
-        <v>91679</v>
+        <v>91682</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>125800829</v>
       </c>
       <c r="B58" t="n">
-        <v>91585</v>
+        <v>91588</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>125807837</v>
       </c>
       <c r="B61" t="n">
-        <v>91922</v>
+        <v>91925</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125833008</v>
+        <v>125833015</v>
       </c>
       <c r="B66" t="n">
-        <v>91228</v>
+        <v>57651</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7332,21 +7332,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478314</v>
+        <v>478373</v>
       </c>
       <c r="R66" t="n">
-        <v>6950373</v>
+        <v>6950375</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7392,6 +7392,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7418,10 +7423,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125833015</v>
+        <v>125833008</v>
       </c>
       <c r="B67" t="n">
-        <v>57651</v>
+        <v>91228</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7429,21 +7434,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7453,10 +7458,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478373</v>
+        <v>478314</v>
       </c>
       <c r="R67" t="n">
-        <v>6950375</v>
+        <v>6950373</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7489,11 +7494,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7620,7 +7620,7 @@
         <v>125833018</v>
       </c>
       <c r="B69" t="n">
-        <v>91679</v>
+        <v>91682</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>125799318</v>
       </c>
       <c r="B72" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -4751,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125802854</v>
+        <v>125800087</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>91228</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478350</v>
+        <v>478329</v>
       </c>
       <c r="R41" t="n">
-        <v>6950427</v>
+        <v>6950196</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,19 +4819,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4846,22 +4836,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125800087</v>
+        <v>125802854</v>
       </c>
       <c r="B42" t="n">
-        <v>91228</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4869,37 +4859,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478329</v>
+        <v>478350</v>
       </c>
       <c r="R42" t="n">
-        <v>6950196</v>
+        <v>6950427</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4926,9 +4916,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,22 +4943,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125802878</v>
+        <v>125797150</v>
       </c>
       <c r="B43" t="n">
-        <v>91524</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4966,37 +4966,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478404</v>
+        <v>478393</v>
       </c>
       <c r="R43" t="n">
-        <v>6950178</v>
+        <v>6950404</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5023,19 +5028,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:15</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5050,22 +5050,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125802862</v>
+        <v>125802883</v>
       </c>
       <c r="B44" t="n">
-        <v>91524</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478280</v>
+        <v>478412</v>
       </c>
       <c r="R44" t="n">
-        <v>6950247</v>
+        <v>6950164</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802863</v>
+        <v>125802878</v>
       </c>
       <c r="B45" t="n">
-        <v>91228</v>
+        <v>91524</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478273</v>
+        <v>478404</v>
       </c>
       <c r="R45" t="n">
-        <v>6950245</v>
+        <v>6950178</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125797150</v>
+        <v>125802862</v>
       </c>
       <c r="B46" t="n">
-        <v>57651</v>
+        <v>91524</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,42 +5287,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478393</v>
+        <v>478280</v>
       </c>
       <c r="R46" t="n">
-        <v>6950404</v>
+        <v>6950247</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5349,14 +5344,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5371,22 +5371,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802883</v>
+        <v>125802863</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>91228</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478412</v>
+        <v>478273</v>
       </c>
       <c r="R47" t="n">
-        <v>6950164</v>
+        <v>6950245</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,10 +5597,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125807838</v>
+        <v>125802867</v>
       </c>
       <c r="B49" t="n">
-        <v>79047</v>
+        <v>78968</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5608,37 +5608,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478276</v>
+        <v>478281</v>
       </c>
       <c r="R49" t="n">
-        <v>6950250</v>
+        <v>6950219</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5665,9 +5665,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5682,22 +5692,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125802867</v>
+        <v>125807838</v>
       </c>
       <c r="B50" t="n">
-        <v>78968</v>
+        <v>79047</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5705,37 +5715,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478281</v>
+        <v>478276</v>
       </c>
       <c r="R50" t="n">
-        <v>6950219</v>
+        <v>6950250</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5762,19 +5772,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5789,57 +5789,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802870</v>
+        <v>125799056</v>
       </c>
       <c r="B51" t="n">
-        <v>98355</v>
+        <v>91228</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478330</v>
+        <v>478298</v>
       </c>
       <c r="R51" t="n">
-        <v>6950181</v>
+        <v>6950374</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5869,19 +5869,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5896,12 +5886,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6209,45 +6199,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125799056</v>
+        <v>125802870</v>
       </c>
       <c r="B55" t="n">
-        <v>91228</v>
+        <v>98355</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478298</v>
+        <v>478330</v>
       </c>
       <c r="R55" t="n">
-        <v>6950374</v>
+        <v>6950181</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6277,9 +6267,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6294,12 +6294,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125833015</v>
+        <v>125833008</v>
       </c>
       <c r="B66" t="n">
-        <v>57651</v>
+        <v>91228</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7332,21 +7332,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478373</v>
+        <v>478314</v>
       </c>
       <c r="R66" t="n">
-        <v>6950375</v>
+        <v>6950373</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7392,11 +7392,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7423,10 +7418,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125833008</v>
+        <v>125833015</v>
       </c>
       <c r="B67" t="n">
-        <v>91228</v>
+        <v>57651</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7434,21 +7429,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7458,10 +7453,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478314</v>
+        <v>478373</v>
       </c>
       <c r="R67" t="n">
-        <v>6950373</v>
+        <v>6950375</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7494,6 +7489,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125800103</v>
+        <v>125798806</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,21 +2902,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478279</v>
+        <v>478289</v>
       </c>
       <c r="R23" t="n">
-        <v>6950281</v>
+        <v>6950427</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2959,24 +2959,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2991,22 +2976,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125798806</v>
+        <v>125800103</v>
       </c>
       <c r="B24" t="n">
-        <v>91228</v>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,21 +2999,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3038,13 +3023,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478289</v>
+        <v>478279</v>
       </c>
       <c r="R24" t="n">
-        <v>6950427</v>
+        <v>6950281</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3071,9 +3056,24 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3088,12 +3088,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3103,7 +3103,7 @@
         <v>125800701</v>
       </c>
       <c r="B25" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125807839</v>
+        <v>125802853</v>
       </c>
       <c r="B26" t="n">
-        <v>78635</v>
+        <v>78378</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,37 +3208,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478450</v>
+        <v>478364</v>
       </c>
       <c r="R26" t="n">
-        <v>6950228</v>
+        <v>6950434</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3265,9 +3265,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3282,22 +3292,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125802853</v>
+        <v>125807839</v>
       </c>
       <c r="B27" t="n">
-        <v>78374</v>
+        <v>78639</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3305,37 +3315,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478364</v>
+        <v>478450</v>
       </c>
       <c r="R27" t="n">
-        <v>6950434</v>
+        <v>6950228</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3362,19 +3372,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3389,64 +3389,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125808994</v>
+        <v>125799925</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>91686</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Klippberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478416</v>
+        <v>478282</v>
       </c>
       <c r="R28" t="n">
-        <v>6950415</v>
+        <v>6950251</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3473,14 +3469,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3495,60 +3496,64 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125799925</v>
+        <v>125808994</v>
       </c>
       <c r="B29" t="n">
-        <v>91682</v>
+        <v>57651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Klippberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478282</v>
+        <v>478416</v>
       </c>
       <c r="R29" t="n">
-        <v>6950251</v>
+        <v>6950415</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3575,19 +3580,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:04</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3602,60 +3602,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125802884</v>
+        <v>125799882</v>
       </c>
       <c r="B30" t="n">
-        <v>98355</v>
+        <v>91232</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478449</v>
+        <v>478301</v>
       </c>
       <c r="R30" t="n">
-        <v>6950182</v>
+        <v>6950180</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3709,60 +3709,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125799882</v>
+        <v>125802884</v>
       </c>
       <c r="B31" t="n">
-        <v>91228</v>
+        <v>98359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478301</v>
+        <v>478449</v>
       </c>
       <c r="R31" t="n">
-        <v>6950180</v>
+        <v>6950182</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3816,44 +3816,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125802868</v>
+        <v>125802866</v>
       </c>
       <c r="B32" t="n">
-        <v>98355</v>
+        <v>91528</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478280</v>
+        <v>478281</v>
       </c>
       <c r="R32" t="n">
-        <v>6950190</v>
+        <v>6950219</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3938,7 +3938,7 @@
         <v>125799436</v>
       </c>
       <c r="B33" t="n">
-        <v>91682</v>
+        <v>91686</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,32 +4032,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125802866</v>
+        <v>125802868</v>
       </c>
       <c r="B34" t="n">
-        <v>91524</v>
+        <v>98359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478281</v>
+        <v>478280</v>
       </c>
       <c r="R34" t="n">
-        <v>6950219</v>
+        <v>6950190</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4142,7 +4142,7 @@
         <v>125802861</v>
       </c>
       <c r="B35" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>125802887</v>
       </c>
       <c r="B36" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>125807835</v>
       </c>
       <c r="B37" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,32 +4450,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125799913</v>
+        <v>125799113</v>
       </c>
       <c r="B38" t="n">
-        <v>91193</v>
+        <v>91528</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478328</v>
+        <v>478286</v>
       </c>
       <c r="R38" t="n">
-        <v>6950173</v>
+        <v>6950325</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4547,32 +4547,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125799113</v>
+        <v>125799913</v>
       </c>
       <c r="B39" t="n">
-        <v>91524</v>
+        <v>91197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478286</v>
+        <v>478328</v>
       </c>
       <c r="R39" t="n">
-        <v>6950325</v>
+        <v>6950173</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4647,7 +4647,7 @@
         <v>125802871</v>
       </c>
       <c r="B40" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>125800087</v>
       </c>
       <c r="B41" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>125802854</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125797150</v>
+        <v>125802878</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>91528</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4966,42 +4966,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478393</v>
+        <v>478404</v>
       </c>
       <c r="R43" t="n">
-        <v>6950404</v>
+        <v>6950178</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5028,14 +5023,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5050,22 +5050,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125802883</v>
+        <v>125802862</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>91528</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478412</v>
+        <v>478280</v>
       </c>
       <c r="R44" t="n">
-        <v>6950164</v>
+        <v>6950247</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802878</v>
+        <v>125802863</v>
       </c>
       <c r="B45" t="n">
-        <v>91524</v>
+        <v>91232</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478404</v>
+        <v>478273</v>
       </c>
       <c r="R45" t="n">
-        <v>6950178</v>
+        <v>6950245</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125802862</v>
+        <v>125802883</v>
       </c>
       <c r="B46" t="n">
-        <v>91524</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478280</v>
+        <v>478412</v>
       </c>
       <c r="R46" t="n">
-        <v>6950247</v>
+        <v>6950164</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802863</v>
+        <v>125797150</v>
       </c>
       <c r="B47" t="n">
-        <v>91228</v>
+        <v>57651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,37 +5394,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478273</v>
+        <v>478393</v>
       </c>
       <c r="R47" t="n">
-        <v>6950245</v>
+        <v>6950404</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5451,19 +5456,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:55</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5478,12 +5478,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5493,7 +5493,7 @@
         <v>125802877</v>
       </c>
       <c r="B48" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125802867</v>
+        <v>125807838</v>
       </c>
       <c r="B49" t="n">
-        <v>78968</v>
+        <v>79051</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5608,37 +5608,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478281</v>
+        <v>478276</v>
       </c>
       <c r="R49" t="n">
-        <v>6950219</v>
+        <v>6950250</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5665,19 +5665,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5692,22 +5682,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125807838</v>
+        <v>125802867</v>
       </c>
       <c r="B50" t="n">
-        <v>79047</v>
+        <v>78972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5715,37 +5705,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478276</v>
+        <v>478281</v>
       </c>
       <c r="R50" t="n">
-        <v>6950250</v>
+        <v>6950219</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5772,9 +5762,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5789,22 +5789,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125799056</v>
+        <v>125800061</v>
       </c>
       <c r="B51" t="n">
-        <v>91228</v>
+        <v>91528</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5812,21 +5812,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478298</v>
+        <v>478319</v>
       </c>
       <c r="R51" t="n">
-        <v>6950374</v>
+        <v>6950199</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125800061</v>
+        <v>125802855</v>
       </c>
       <c r="B52" t="n">
-        <v>91524</v>
+        <v>78378</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5909,37 +5909,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478319</v>
+        <v>478311</v>
       </c>
       <c r="R52" t="n">
-        <v>6950199</v>
+        <v>6950419</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5966,9 +5966,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5983,22 +5993,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125802855</v>
+        <v>125807840</v>
       </c>
       <c r="B53" t="n">
-        <v>78374</v>
+        <v>78378</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6026,17 +6036,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478311</v>
+        <v>478314</v>
       </c>
       <c r="R53" t="n">
-        <v>6950419</v>
+        <v>6950423</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6063,19 +6073,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6090,22 +6090,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125807840</v>
+        <v>125799056</v>
       </c>
       <c r="B54" t="n">
-        <v>78374</v>
+        <v>91232</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6113,34 +6113,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478314</v>
+        <v>478298</v>
       </c>
       <c r="R54" t="n">
-        <v>6950423</v>
+        <v>6950374</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6187,12 +6187,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6202,7 +6202,7 @@
         <v>125802870</v>
       </c>
       <c r="B55" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6306,32 +6306,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125799789</v>
+        <v>125800829</v>
       </c>
       <c r="B56" t="n">
-        <v>91242</v>
+        <v>91592</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>2063</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478279</v>
+        <v>478489</v>
       </c>
       <c r="R56" t="n">
-        <v>6950281</v>
+        <v>6950236</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6374,19 +6374,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6401,44 +6391,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125795897</v>
+        <v>125799789</v>
       </c>
       <c r="B57" t="n">
-        <v>91682</v>
+        <v>91246</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6448,13 +6438,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478293</v>
+        <v>478279</v>
       </c>
       <c r="R57" t="n">
-        <v>6950485</v>
+        <v>6950281</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6481,9 +6471,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6498,22 +6498,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125800829</v>
+        <v>125795897</v>
       </c>
       <c r="B58" t="n">
-        <v>91588</v>
+        <v>91686</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2063</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478489</v>
+        <v>478293</v>
       </c>
       <c r="R58" t="n">
-        <v>6950236</v>
+        <v>6950485</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6610,7 +6610,7 @@
         <v>125802858</v>
       </c>
       <c r="B59" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>125802875</v>
       </c>
       <c r="B60" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>125807837</v>
       </c>
       <c r="B61" t="n">
-        <v>91925</v>
+        <v>91929</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>125802859</v>
       </c>
       <c r="B62" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>125797369</v>
       </c>
       <c r="B63" t="n">
-        <v>78992</v>
+        <v>78996</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>125833009</v>
       </c>
       <c r="B64" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>125833008</v>
       </c>
       <c r="B66" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>125833006</v>
       </c>
       <c r="B68" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>125833018</v>
       </c>
       <c r="B69" t="n">
-        <v>91682</v>
+        <v>91686</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>125833007</v>
       </c>
       <c r="B70" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>125799318</v>
       </c>
       <c r="B72" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125798806</v>
+        <v>125800103</v>
       </c>
       <c r="B23" t="n">
-        <v>91232</v>
+        <v>57651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,21 +2902,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478289</v>
+        <v>478279</v>
       </c>
       <c r="R23" t="n">
-        <v>6950427</v>
+        <v>6950281</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2959,9 +2959,24 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,22 +2991,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125800103</v>
+        <v>125798806</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,21 +3014,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3023,13 +3038,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478279</v>
+        <v>478289</v>
       </c>
       <c r="R24" t="n">
-        <v>6950281</v>
+        <v>6950427</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3056,24 +3071,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3088,12 +3088,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125800087</v>
+        <v>125802854</v>
       </c>
       <c r="B41" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478329</v>
+        <v>478350</v>
       </c>
       <c r="R41" t="n">
-        <v>6950196</v>
+        <v>6950427</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,9 +4819,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4836,22 +4846,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125802854</v>
+        <v>125800087</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4859,37 +4869,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478350</v>
+        <v>478329</v>
       </c>
       <c r="R42" t="n">
-        <v>6950427</v>
+        <v>6950196</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4916,19 +4926,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,12 +4943,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -6306,32 +6306,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125800829</v>
+        <v>125799789</v>
       </c>
       <c r="B56" t="n">
-        <v>91592</v>
+        <v>91246</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2063</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478489</v>
+        <v>478279</v>
       </c>
       <c r="R56" t="n">
-        <v>6950236</v>
+        <v>6950281</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6374,9 +6374,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6391,44 +6401,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125799789</v>
+        <v>125795897</v>
       </c>
       <c r="B57" t="n">
-        <v>91246</v>
+        <v>91686</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6438,13 +6448,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478279</v>
+        <v>478293</v>
       </c>
       <c r="R57" t="n">
-        <v>6950281</v>
+        <v>6950485</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6471,19 +6481,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6498,22 +6498,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125795897</v>
+        <v>125800829</v>
       </c>
       <c r="B58" t="n">
-        <v>91686</v>
+        <v>91592</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>2063</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478293</v>
+        <v>478489</v>
       </c>
       <c r="R58" t="n">
-        <v>6950485</v>
+        <v>6950236</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125800103</v>
+        <v>125798806</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,21 +2902,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478279</v>
+        <v>478289</v>
       </c>
       <c r="R23" t="n">
-        <v>6950281</v>
+        <v>6950427</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2959,24 +2959,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2991,22 +2976,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125798806</v>
+        <v>125800103</v>
       </c>
       <c r="B24" t="n">
-        <v>91232</v>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,21 +2999,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3038,13 +3023,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478289</v>
+        <v>478279</v>
       </c>
       <c r="R24" t="n">
-        <v>6950427</v>
+        <v>6950281</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3071,9 +3056,24 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3088,12 +3088,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125802853</v>
+        <v>125807839</v>
       </c>
       <c r="B26" t="n">
-        <v>78378</v>
+        <v>78639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,37 +3208,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478364</v>
+        <v>478450</v>
       </c>
       <c r="R26" t="n">
-        <v>6950434</v>
+        <v>6950228</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3265,19 +3265,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3292,22 +3282,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125807839</v>
+        <v>125802853</v>
       </c>
       <c r="B27" t="n">
-        <v>78639</v>
+        <v>78378</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3315,37 +3305,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478450</v>
+        <v>478364</v>
       </c>
       <c r="R27" t="n">
-        <v>6950228</v>
+        <v>6950434</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3372,9 +3362,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3389,12 +3389,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3724,7 +3724,7 @@
         <v>125802884</v>
       </c>
       <c r="B31" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3828,48 +3828,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125802866</v>
+        <v>125799436</v>
       </c>
       <c r="B32" t="n">
-        <v>91528</v>
+        <v>91686</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
         <v>478281</v>
       </c>
       <c r="R32" t="n">
-        <v>6950219</v>
+        <v>6950242</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3896,19 +3896,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3923,60 +3913,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125799436</v>
+        <v>125802866</v>
       </c>
       <c r="B33" t="n">
-        <v>91686</v>
+        <v>91528</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
         <v>478281</v>
       </c>
       <c r="R33" t="n">
-        <v>6950242</v>
+        <v>6950219</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4003,9 +3993,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4020,12 +4020,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4035,7 +4035,7 @@
         <v>125802868</v>
       </c>
       <c r="B34" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4353,45 +4353,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125807835</v>
+        <v>125799913</v>
       </c>
       <c r="B37" t="n">
-        <v>79561</v>
+        <v>91197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478334</v>
+        <v>478328</v>
       </c>
       <c r="R37" t="n">
-        <v>6950420</v>
+        <v>6950173</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4438,12 +4438,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4547,45 +4547,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125799913</v>
+        <v>125807835</v>
       </c>
       <c r="B39" t="n">
-        <v>91197</v>
+        <v>79561</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478328</v>
+        <v>478334</v>
       </c>
       <c r="R39" t="n">
-        <v>6950173</v>
+        <v>6950420</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4632,12 +4632,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125802854</v>
+        <v>125800087</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478350</v>
+        <v>478329</v>
       </c>
       <c r="R41" t="n">
-        <v>6950427</v>
+        <v>6950196</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,19 +4819,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4846,22 +4836,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125800087</v>
+        <v>125802854</v>
       </c>
       <c r="B42" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4869,37 +4859,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478329</v>
+        <v>478350</v>
       </c>
       <c r="R42" t="n">
-        <v>6950196</v>
+        <v>6950427</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4926,9 +4916,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,22 +4943,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125802878</v>
+        <v>125797150</v>
       </c>
       <c r="B43" t="n">
-        <v>91528</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4966,37 +4966,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478404</v>
+        <v>478393</v>
       </c>
       <c r="R43" t="n">
-        <v>6950178</v>
+        <v>6950404</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5023,19 +5028,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:15</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5050,22 +5050,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125802862</v>
+        <v>125802883</v>
       </c>
       <c r="B44" t="n">
-        <v>91528</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478280</v>
+        <v>478412</v>
       </c>
       <c r="R44" t="n">
-        <v>6950247</v>
+        <v>6950164</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802863</v>
+        <v>125802878</v>
       </c>
       <c r="B45" t="n">
-        <v>91232</v>
+        <v>91528</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478273</v>
+        <v>478404</v>
       </c>
       <c r="R45" t="n">
-        <v>6950245</v>
+        <v>6950178</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125802883</v>
+        <v>125802862</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>91528</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478412</v>
+        <v>478280</v>
       </c>
       <c r="R46" t="n">
-        <v>6950164</v>
+        <v>6950247</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125797150</v>
+        <v>125802863</v>
       </c>
       <c r="B47" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,42 +5394,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478393</v>
+        <v>478273</v>
       </c>
       <c r="R47" t="n">
-        <v>6950404</v>
+        <v>6950245</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5456,14 +5451,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5478,12 +5478,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5493,7 +5493,7 @@
         <v>125802877</v>
       </c>
       <c r="B48" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125807838</v>
+        <v>125802867</v>
       </c>
       <c r="B49" t="n">
-        <v>79051</v>
+        <v>78972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5608,37 +5608,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478276</v>
+        <v>478281</v>
       </c>
       <c r="R49" t="n">
-        <v>6950250</v>
+        <v>6950219</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5665,9 +5665,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5682,22 +5692,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125802867</v>
+        <v>125807838</v>
       </c>
       <c r="B50" t="n">
-        <v>78972</v>
+        <v>79051</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5705,37 +5715,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478281</v>
+        <v>478276</v>
       </c>
       <c r="R50" t="n">
-        <v>6950219</v>
+        <v>6950250</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5762,19 +5772,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5789,22 +5789,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125800061</v>
+        <v>125799056</v>
       </c>
       <c r="B51" t="n">
-        <v>91528</v>
+        <v>91232</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5812,21 +5812,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478319</v>
+        <v>478298</v>
       </c>
       <c r="R51" t="n">
-        <v>6950199</v>
+        <v>6950374</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5898,7 +5898,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802855</v>
+        <v>125807840</v>
       </c>
       <c r="B52" t="n">
         <v>78378</v>
@@ -5929,17 +5929,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478311</v>
+        <v>478314</v>
       </c>
       <c r="R52" t="n">
-        <v>6950419</v>
+        <v>6950423</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5966,19 +5966,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5993,19 +5983,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125807840</v>
+        <v>125802855</v>
       </c>
       <c r="B53" t="n">
         <v>78378</v>
@@ -6036,17 +6026,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478314</v>
+        <v>478311</v>
       </c>
       <c r="R53" t="n">
-        <v>6950423</v>
+        <v>6950419</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6073,9 +6063,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6090,22 +6090,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125799056</v>
+        <v>125800061</v>
       </c>
       <c r="B54" t="n">
-        <v>91232</v>
+        <v>91528</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6113,21 +6113,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478298</v>
+        <v>478319</v>
       </c>
       <c r="R54" t="n">
-        <v>6950374</v>
+        <v>6950199</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6202,7 +6202,7 @@
         <v>125802870</v>
       </c>
       <c r="B55" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>125799318</v>
       </c>
       <c r="B72" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -4751,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125800087</v>
+        <v>125802854</v>
       </c>
       <c r="B41" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478329</v>
+        <v>478350</v>
       </c>
       <c r="R41" t="n">
-        <v>6950196</v>
+        <v>6950427</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,9 +4819,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4836,22 +4846,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125802854</v>
+        <v>125800087</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4859,37 +4869,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478350</v>
+        <v>478329</v>
       </c>
       <c r="R42" t="n">
-        <v>6950427</v>
+        <v>6950196</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4916,19 +4926,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,12 +4943,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -3401,48 +3401,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125799925</v>
+        <v>125808994</v>
       </c>
       <c r="B28" t="n">
-        <v>91686</v>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Klippberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478282</v>
+        <v>478416</v>
       </c>
       <c r="R28" t="n">
-        <v>6950251</v>
+        <v>6950415</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3469,19 +3473,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:04</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3496,64 +3495,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125808994</v>
+        <v>125799925</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>91686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Klippberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478416</v>
+        <v>478282</v>
       </c>
       <c r="R29" t="n">
-        <v>6950415</v>
+        <v>6950251</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3580,14 +3575,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3602,12 +3602,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3828,48 +3828,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125799436</v>
+        <v>125802868</v>
       </c>
       <c r="B32" t="n">
-        <v>91686</v>
+        <v>98360</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478281</v>
+        <v>478280</v>
       </c>
       <c r="R32" t="n">
-        <v>6950242</v>
+        <v>6950190</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3896,9 +3896,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3913,60 +3923,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125802866</v>
+        <v>125799436</v>
       </c>
       <c r="B33" t="n">
-        <v>91528</v>
+        <v>91686</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
         <v>478281</v>
       </c>
       <c r="R33" t="n">
-        <v>6950219</v>
+        <v>6950242</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3993,19 +4003,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4020,44 +4020,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125802868</v>
+        <v>125802866</v>
       </c>
       <c r="B34" t="n">
-        <v>98360</v>
+        <v>91528</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478280</v>
+        <v>478281</v>
       </c>
       <c r="R34" t="n">
-        <v>6950190</v>
+        <v>6950219</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5062,32 +5062,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125802883</v>
+        <v>125802877</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478412</v>
+        <v>478396</v>
       </c>
       <c r="R44" t="n">
-        <v>6950164</v>
+        <v>6950183</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802878</v>
+        <v>125802883</v>
       </c>
       <c r="B45" t="n">
-        <v>91528</v>
+        <v>78972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478404</v>
+        <v>478412</v>
       </c>
       <c r="R45" t="n">
-        <v>6950178</v>
+        <v>6950164</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,7 +5276,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125802862</v>
+        <v>125802878</v>
       </c>
       <c r="B46" t="n">
         <v>91528</v>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478280</v>
+        <v>478404</v>
       </c>
       <c r="R46" t="n">
-        <v>6950247</v>
+        <v>6950178</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802863</v>
+        <v>125802862</v>
       </c>
       <c r="B47" t="n">
-        <v>91232</v>
+        <v>91528</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478273</v>
+        <v>478280</v>
       </c>
       <c r="R47" t="n">
-        <v>6950245</v>
+        <v>6950247</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125802877</v>
+        <v>125802863</v>
       </c>
       <c r="B48" t="n">
-        <v>98360</v>
+        <v>91232</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478396</v>
+        <v>478273</v>
       </c>
       <c r="R48" t="n">
-        <v>6950183</v>
+        <v>6950245</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6714,48 +6714,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125802875</v>
+        <v>125807837</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>91929</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478367</v>
+        <v>478281</v>
       </c>
       <c r="R60" t="n">
-        <v>6950197</v>
+        <v>6950244</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6782,19 +6782,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6809,60 +6799,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125807837</v>
+        <v>125802875</v>
       </c>
       <c r="B61" t="n">
-        <v>91929</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478281</v>
+        <v>478367</v>
       </c>
       <c r="R61" t="n">
-        <v>6950244</v>
+        <v>6950197</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6889,9 +6879,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6906,12 +6906,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -2682,7 +2682,7 @@
         <v>125657692</v>
       </c>
       <c r="B21" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>125657691</v>
       </c>
       <c r="B22" t="n">
-        <v>57755</v>
+        <v>57756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>125798806</v>
       </c>
       <c r="B23" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>125800103</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>125800701</v>
       </c>
       <c r="B25" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>125807839</v>
       </c>
       <c r="B26" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>125802853</v>
       </c>
       <c r="B27" t="n">
-        <v>78378</v>
+        <v>78379</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,52 +3401,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125808994</v>
+        <v>125799925</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>91688</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Klippberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478416</v>
+        <v>478282</v>
       </c>
       <c r="R28" t="n">
-        <v>6950415</v>
+        <v>6950251</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3473,14 +3469,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3495,60 +3496,64 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125799925</v>
+        <v>125808994</v>
       </c>
       <c r="B29" t="n">
-        <v>91686</v>
+        <v>57652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Klippberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478282</v>
+        <v>478416</v>
       </c>
       <c r="R29" t="n">
-        <v>6950251</v>
+        <v>6950415</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3575,19 +3580,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:04</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3602,12 +3602,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3617,7 +3617,7 @@
         <v>125799882</v>
       </c>
       <c r="B30" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>125802884</v>
       </c>
       <c r="B31" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3828,32 +3828,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125802868</v>
+        <v>125802866</v>
       </c>
       <c r="B32" t="n">
-        <v>98360</v>
+        <v>91530</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478280</v>
+        <v>478281</v>
       </c>
       <c r="R32" t="n">
-        <v>6950190</v>
+        <v>6950219</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3938,7 +3938,7 @@
         <v>125799436</v>
       </c>
       <c r="B33" t="n">
-        <v>91686</v>
+        <v>91688</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,32 +4032,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125802866</v>
+        <v>125802868</v>
       </c>
       <c r="B34" t="n">
-        <v>91528</v>
+        <v>98362</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478281</v>
+        <v>478280</v>
       </c>
       <c r="R34" t="n">
-        <v>6950219</v>
+        <v>6950190</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4142,7 +4142,7 @@
         <v>125802861</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>125802887</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4353,32 +4353,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125799913</v>
+        <v>125799113</v>
       </c>
       <c r="B37" t="n">
-        <v>91197</v>
+        <v>91530</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478328</v>
+        <v>478286</v>
       </c>
       <c r="R37" t="n">
-        <v>6950173</v>
+        <v>6950325</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4450,32 +4450,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125799113</v>
+        <v>125799913</v>
       </c>
       <c r="B38" t="n">
-        <v>91528</v>
+        <v>91199</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478286</v>
+        <v>478328</v>
       </c>
       <c r="R38" t="n">
-        <v>6950325</v>
+        <v>6950173</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4550,7 +4550,7 @@
         <v>125807835</v>
       </c>
       <c r="B39" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>125802871</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125802854</v>
+        <v>125800087</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>91234</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478350</v>
+        <v>478329</v>
       </c>
       <c r="R41" t="n">
-        <v>6950427</v>
+        <v>6950196</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,19 +4819,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4846,22 +4836,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125800087</v>
+        <v>125802854</v>
       </c>
       <c r="B42" t="n">
-        <v>91232</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4869,37 +4859,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478329</v>
+        <v>478350</v>
       </c>
       <c r="R42" t="n">
-        <v>6950196</v>
+        <v>6950427</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4926,9 +4916,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,22 +4943,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125797150</v>
+        <v>125802878</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>91530</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4966,42 +4966,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478393</v>
+        <v>478404</v>
       </c>
       <c r="R43" t="n">
-        <v>6950404</v>
+        <v>6950178</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5028,14 +5023,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5050,44 +5050,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125802877</v>
+        <v>125802862</v>
       </c>
       <c r="B44" t="n">
-        <v>98360</v>
+        <v>91530</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478396</v>
+        <v>478280</v>
       </c>
       <c r="R44" t="n">
-        <v>6950183</v>
+        <v>6950247</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5172,7 +5172,7 @@
         <v>125802883</v>
       </c>
       <c r="B45" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125802878</v>
+        <v>125797150</v>
       </c>
       <c r="B46" t="n">
-        <v>91528</v>
+        <v>57652</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,37 +5287,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478404</v>
+        <v>478393</v>
       </c>
       <c r="R46" t="n">
-        <v>6950178</v>
+        <v>6950404</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5344,19 +5349,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:15</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5371,22 +5371,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802862</v>
+        <v>125802863</v>
       </c>
       <c r="B47" t="n">
-        <v>91528</v>
+        <v>91234</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478280</v>
+        <v>478273</v>
       </c>
       <c r="R47" t="n">
-        <v>6950247</v>
+        <v>6950245</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125802863</v>
+        <v>125802877</v>
       </c>
       <c r="B48" t="n">
-        <v>91232</v>
+        <v>98362</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478273</v>
+        <v>478396</v>
       </c>
       <c r="R48" t="n">
-        <v>6950245</v>
+        <v>6950183</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5600,7 +5600,7 @@
         <v>125802867</v>
       </c>
       <c r="B49" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>125807838</v>
       </c>
       <c r="B50" t="n">
-        <v>79051</v>
+        <v>79052</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,45 +5801,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125799056</v>
+        <v>125802870</v>
       </c>
       <c r="B51" t="n">
-        <v>91232</v>
+        <v>98362</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478298</v>
+        <v>478330</v>
       </c>
       <c r="R51" t="n">
-        <v>6950374</v>
+        <v>6950181</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5869,9 +5869,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5886,22 +5896,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125807840</v>
+        <v>125800061</v>
       </c>
       <c r="B52" t="n">
-        <v>78378</v>
+        <v>91530</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5909,34 +5919,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478314</v>
+        <v>478319</v>
       </c>
       <c r="R52" t="n">
-        <v>6950423</v>
+        <v>6950199</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5983,12 +5993,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5998,7 +6008,7 @@
         <v>125802855</v>
       </c>
       <c r="B53" t="n">
-        <v>78378</v>
+        <v>78379</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6102,10 +6112,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125800061</v>
+        <v>125807840</v>
       </c>
       <c r="B54" t="n">
-        <v>91528</v>
+        <v>78379</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6113,34 +6123,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478319</v>
+        <v>478314</v>
       </c>
       <c r="R54" t="n">
-        <v>6950199</v>
+        <v>6950423</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6187,57 +6197,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125802870</v>
+        <v>125799056</v>
       </c>
       <c r="B55" t="n">
-        <v>98360</v>
+        <v>91234</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478330</v>
+        <v>478298</v>
       </c>
       <c r="R55" t="n">
-        <v>6950181</v>
+        <v>6950374</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6267,19 +6277,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6294,44 +6294,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125799789</v>
+        <v>125800829</v>
       </c>
       <c r="B56" t="n">
-        <v>91246</v>
+        <v>91594</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>2063</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478279</v>
+        <v>478489</v>
       </c>
       <c r="R56" t="n">
-        <v>6950281</v>
+        <v>6950236</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6374,19 +6374,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6401,44 +6391,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125795897</v>
+        <v>125799789</v>
       </c>
       <c r="B57" t="n">
-        <v>91686</v>
+        <v>91248</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6448,13 +6438,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478293</v>
+        <v>478279</v>
       </c>
       <c r="R57" t="n">
-        <v>6950485</v>
+        <v>6950281</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6481,9 +6471,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6498,22 +6498,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125800829</v>
+        <v>125795897</v>
       </c>
       <c r="B58" t="n">
-        <v>91592</v>
+        <v>91688</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2063</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478489</v>
+        <v>478293</v>
       </c>
       <c r="R58" t="n">
-        <v>6950236</v>
+        <v>6950485</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6610,7 +6610,7 @@
         <v>125802858</v>
       </c>
       <c r="B59" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>125807837</v>
       </c>
       <c r="B60" t="n">
-        <v>91929</v>
+        <v>91931</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>125802875</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>125802859</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>125797369</v>
       </c>
       <c r="B63" t="n">
-        <v>78996</v>
+        <v>78997</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>125833009</v>
       </c>
       <c r="B64" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>125833014</v>
       </c>
       <c r="B65" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>125833008</v>
       </c>
       <c r="B66" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>125833015</v>
       </c>
       <c r="B67" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>125833006</v>
       </c>
       <c r="B68" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>125833018</v>
       </c>
       <c r="B69" t="n">
-        <v>91686</v>
+        <v>91688</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>125833007</v>
       </c>
       <c r="B70" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>125833013</v>
       </c>
       <c r="B71" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>125799318</v>
       </c>
       <c r="B72" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -3828,32 +3828,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125802866</v>
+        <v>125802868</v>
       </c>
       <c r="B32" t="n">
-        <v>91530</v>
+        <v>98362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478281</v>
+        <v>478280</v>
       </c>
       <c r="R32" t="n">
-        <v>6950219</v>
+        <v>6950190</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3935,48 +3935,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125799436</v>
+        <v>125802866</v>
       </c>
       <c r="B33" t="n">
-        <v>91688</v>
+        <v>91530</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
         <v>478281</v>
       </c>
       <c r="R33" t="n">
-        <v>6950242</v>
+        <v>6950219</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4003,9 +4003,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4020,60 +4030,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125802868</v>
+        <v>125799436</v>
       </c>
       <c r="B34" t="n">
-        <v>98362</v>
+        <v>91688</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478280</v>
+        <v>478281</v>
       </c>
       <c r="R34" t="n">
-        <v>6950190</v>
+        <v>6950242</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4100,19 +4110,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4127,12 +4127,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125797150</v>
+        <v>125802863</v>
       </c>
       <c r="B46" t="n">
-        <v>57652</v>
+        <v>91234</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,42 +5287,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478393</v>
+        <v>478273</v>
       </c>
       <c r="R46" t="n">
-        <v>6950404</v>
+        <v>6950245</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5349,14 +5344,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5371,44 +5371,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802863</v>
+        <v>125802877</v>
       </c>
       <c r="B47" t="n">
-        <v>91234</v>
+        <v>98362</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478273</v>
+        <v>478396</v>
       </c>
       <c r="R47" t="n">
-        <v>6950245</v>
+        <v>6950183</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5490,48 +5490,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125802877</v>
+        <v>125797150</v>
       </c>
       <c r="B48" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478396</v>
+        <v>478393</v>
       </c>
       <c r="R48" t="n">
-        <v>6950183</v>
+        <v>6950404</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5558,19 +5563,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5585,12 +5585,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125800061</v>
+        <v>125799056</v>
       </c>
       <c r="B52" t="n">
-        <v>91530</v>
+        <v>91234</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5919,21 +5919,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5943,10 +5943,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478319</v>
+        <v>478298</v>
       </c>
       <c r="R52" t="n">
-        <v>6950199</v>
+        <v>6950374</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6005,10 +6005,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125802855</v>
+        <v>125800061</v>
       </c>
       <c r="B53" t="n">
-        <v>78379</v>
+        <v>91530</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6016,37 +6016,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478311</v>
+        <v>478319</v>
       </c>
       <c r="R53" t="n">
-        <v>6950419</v>
+        <v>6950199</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6073,19 +6073,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6100,19 +6090,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125807840</v>
+        <v>125802855</v>
       </c>
       <c r="B54" t="n">
         <v>78379</v>
@@ -6143,17 +6133,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478314</v>
+        <v>478311</v>
       </c>
       <c r="R54" t="n">
-        <v>6950423</v>
+        <v>6950419</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6180,9 +6170,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6197,22 +6197,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125799056</v>
+        <v>125807840</v>
       </c>
       <c r="B55" t="n">
-        <v>91234</v>
+        <v>78379</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6220,34 +6220,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478298</v>
+        <v>478314</v>
       </c>
       <c r="R55" t="n">
-        <v>6950374</v>
+        <v>6950423</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6294,12 +6294,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125798806</v>
+        <v>125800103</v>
       </c>
       <c r="B23" t="n">
-        <v>91234</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,21 +2902,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478289</v>
+        <v>478279</v>
       </c>
       <c r="R23" t="n">
-        <v>6950427</v>
+        <v>6950281</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2959,9 +2959,24 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,22 +2991,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125800103</v>
+        <v>125798806</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>91236</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,21 +3014,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3023,13 +3038,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478279</v>
+        <v>478289</v>
       </c>
       <c r="R24" t="n">
-        <v>6950281</v>
+        <v>6950427</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3056,24 +3071,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3088,12 +3088,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3404,7 +3404,7 @@
         <v>125799925</v>
       </c>
       <c r="B28" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>125799882</v>
       </c>
       <c r="B30" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>125802884</v>
       </c>
       <c r="B31" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3828,48 +3828,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125802868</v>
+        <v>125799436</v>
       </c>
       <c r="B32" t="n">
-        <v>98362</v>
+        <v>91690</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478280</v>
+        <v>478281</v>
       </c>
       <c r="R32" t="n">
-        <v>6950190</v>
+        <v>6950242</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3896,19 +3896,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3923,12 +3913,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3938,7 +3928,7 @@
         <v>125802866</v>
       </c>
       <c r="B33" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4042,48 +4032,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125799436</v>
+        <v>125802868</v>
       </c>
       <c r="B34" t="n">
-        <v>91688</v>
+        <v>98364</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478281</v>
+        <v>478280</v>
       </c>
       <c r="R34" t="n">
-        <v>6950242</v>
+        <v>6950190</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4110,9 +4100,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4127,12 +4127,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
         <v>125799113</v>
       </c>
       <c r="B37" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,45 +4450,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125799913</v>
+        <v>125807835</v>
       </c>
       <c r="B38" t="n">
-        <v>91199</v>
+        <v>79562</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478328</v>
+        <v>478334</v>
       </c>
       <c r="R38" t="n">
-        <v>6950173</v>
+        <v>6950420</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4535,57 +4535,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125807835</v>
+        <v>125799913</v>
       </c>
       <c r="B39" t="n">
-        <v>79562</v>
+        <v>91201</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478334</v>
+        <v>478328</v>
       </c>
       <c r="R39" t="n">
-        <v>6950420</v>
+        <v>6950173</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4632,12 +4632,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4754,7 +4754,7 @@
         <v>125800087</v>
       </c>
       <c r="B41" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,32 +4955,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125802878</v>
+        <v>125802877</v>
       </c>
       <c r="B43" t="n">
-        <v>91530</v>
+        <v>98364</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478404</v>
+        <v>478396</v>
       </c>
       <c r="R43" t="n">
-        <v>6950178</v>
+        <v>6950183</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5062,10 +5062,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125802862</v>
+        <v>125797150</v>
       </c>
       <c r="B44" t="n">
-        <v>91530</v>
+        <v>57652</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5073,37 +5073,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478280</v>
+        <v>478393</v>
       </c>
       <c r="R44" t="n">
-        <v>6950247</v>
+        <v>6950404</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5130,19 +5135,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:50</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5157,22 +5157,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802883</v>
+        <v>125802878</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>91532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478412</v>
+        <v>478404</v>
       </c>
       <c r="R45" t="n">
-        <v>6950164</v>
+        <v>6950178</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125802863</v>
+        <v>125802862</v>
       </c>
       <c r="B46" t="n">
-        <v>91234</v>
+        <v>91532</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478273</v>
+        <v>478280</v>
       </c>
       <c r="R46" t="n">
-        <v>6950245</v>
+        <v>6950247</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5383,32 +5383,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802877</v>
+        <v>125802863</v>
       </c>
       <c r="B47" t="n">
-        <v>98362</v>
+        <v>91236</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478396</v>
+        <v>478273</v>
       </c>
       <c r="R47" t="n">
-        <v>6950183</v>
+        <v>6950245</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125797150</v>
+        <v>125802883</v>
       </c>
       <c r="B48" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5501,42 +5501,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478393</v>
+        <v>478412</v>
       </c>
       <c r="R48" t="n">
-        <v>6950404</v>
+        <v>6950164</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5563,14 +5558,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5585,22 +5585,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125802867</v>
+        <v>125807838</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>79052</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5608,37 +5608,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478281</v>
+        <v>478276</v>
       </c>
       <c r="R49" t="n">
-        <v>6950219</v>
+        <v>6950250</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5665,19 +5665,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5692,22 +5682,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125807838</v>
+        <v>125802867</v>
       </c>
       <c r="B50" t="n">
-        <v>79052</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5715,37 +5705,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478276</v>
+        <v>478281</v>
       </c>
       <c r="R50" t="n">
-        <v>6950250</v>
+        <v>6950219</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5772,9 +5762,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5789,57 +5789,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802870</v>
+        <v>125799056</v>
       </c>
       <c r="B51" t="n">
-        <v>98362</v>
+        <v>91236</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478330</v>
+        <v>478298</v>
       </c>
       <c r="R51" t="n">
-        <v>6950181</v>
+        <v>6950374</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5869,19 +5869,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5896,22 +5886,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125799056</v>
+        <v>125800061</v>
       </c>
       <c r="B52" t="n">
-        <v>91234</v>
+        <v>91532</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5919,21 +5909,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5943,10 +5933,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478298</v>
+        <v>478319</v>
       </c>
       <c r="R52" t="n">
-        <v>6950374</v>
+        <v>6950199</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6005,10 +5995,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125800061</v>
+        <v>125807840</v>
       </c>
       <c r="B53" t="n">
-        <v>91530</v>
+        <v>78379</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6016,34 +6006,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478319</v>
+        <v>478314</v>
       </c>
       <c r="R53" t="n">
-        <v>6950199</v>
+        <v>6950423</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6090,12 +6080,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6209,45 +6199,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125807840</v>
+        <v>125802870</v>
       </c>
       <c r="B55" t="n">
-        <v>78379</v>
+        <v>98364</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478314</v>
+        <v>478330</v>
       </c>
       <c r="R55" t="n">
-        <v>6950423</v>
+        <v>6950181</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6277,9 +6267,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6294,44 +6294,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125800829</v>
+        <v>125799789</v>
       </c>
       <c r="B56" t="n">
-        <v>91594</v>
+        <v>91250</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2063</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478489</v>
+        <v>478279</v>
       </c>
       <c r="R56" t="n">
-        <v>6950236</v>
+        <v>6950281</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6374,9 +6374,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6391,44 +6401,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125799789</v>
+        <v>125795897</v>
       </c>
       <c r="B57" t="n">
-        <v>91248</v>
+        <v>91690</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6438,13 +6448,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478279</v>
+        <v>478293</v>
       </c>
       <c r="R57" t="n">
-        <v>6950281</v>
+        <v>6950485</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6471,19 +6481,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6498,22 +6498,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125795897</v>
+        <v>125800829</v>
       </c>
       <c r="B58" t="n">
-        <v>91688</v>
+        <v>91596</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>2063</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478293</v>
+        <v>478489</v>
       </c>
       <c r="R58" t="n">
-        <v>6950485</v>
+        <v>6950236</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6717,7 +6717,7 @@
         <v>125807837</v>
       </c>
       <c r="B60" t="n">
-        <v>91931</v>
+        <v>91933</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>125833009</v>
       </c>
       <c r="B64" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125833008</v>
+        <v>125833015</v>
       </c>
       <c r="B66" t="n">
-        <v>91234</v>
+        <v>57652</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7332,21 +7332,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478314</v>
+        <v>478373</v>
       </c>
       <c r="R66" t="n">
-        <v>6950373</v>
+        <v>6950375</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7392,6 +7392,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7418,10 +7423,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125833015</v>
+        <v>125833008</v>
       </c>
       <c r="B67" t="n">
-        <v>57652</v>
+        <v>91236</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7429,21 +7434,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7453,10 +7458,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478373</v>
+        <v>478314</v>
       </c>
       <c r="R67" t="n">
-        <v>6950375</v>
+        <v>6950373</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7489,11 +7494,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7523,7 +7523,7 @@
         <v>125833006</v>
       </c>
       <c r="B68" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>125833018</v>
       </c>
       <c r="B69" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>125833007</v>
       </c>
       <c r="B70" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>125799318</v>
       </c>
       <c r="B72" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125800103</v>
+        <v>125798806</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>91236</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,21 +2902,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478279</v>
+        <v>478289</v>
       </c>
       <c r="R23" t="n">
-        <v>6950281</v>
+        <v>6950427</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2959,24 +2959,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2991,22 +2976,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125798806</v>
+        <v>125800103</v>
       </c>
       <c r="B24" t="n">
-        <v>91236</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,21 +2999,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3038,13 +3023,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478289</v>
+        <v>478279</v>
       </c>
       <c r="R24" t="n">
-        <v>6950427</v>
+        <v>6950281</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3071,9 +3056,24 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3088,12 +3088,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -2894,7 +2894,7 @@
         <v>125798806</v>
       </c>
       <c r="B23" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125807839</v>
+        <v>125802853</v>
       </c>
       <c r="B26" t="n">
-        <v>78640</v>
+        <v>78379</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,37 +3208,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478450</v>
+        <v>478364</v>
       </c>
       <c r="R26" t="n">
-        <v>6950228</v>
+        <v>6950434</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3265,9 +3265,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3282,22 +3292,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125802853</v>
+        <v>125807839</v>
       </c>
       <c r="B27" t="n">
-        <v>78379</v>
+        <v>78640</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3305,37 +3315,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478364</v>
+        <v>478450</v>
       </c>
       <c r="R27" t="n">
-        <v>6950434</v>
+        <v>6950228</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3362,19 +3372,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3389,12 +3389,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3404,7 +3404,7 @@
         <v>125799925</v>
       </c>
       <c r="B28" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3614,48 +3614,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125799882</v>
+        <v>125802884</v>
       </c>
       <c r="B30" t="n">
-        <v>91236</v>
+        <v>98366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478301</v>
+        <v>478449</v>
       </c>
       <c r="R30" t="n">
-        <v>6950180</v>
+        <v>6950182</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3709,60 +3709,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125802884</v>
+        <v>125799882</v>
       </c>
       <c r="B31" t="n">
-        <v>98364</v>
+        <v>91238</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478449</v>
+        <v>478301</v>
       </c>
       <c r="R31" t="n">
-        <v>6950182</v>
+        <v>6950180</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3816,12 +3816,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
         <v>125799436</v>
       </c>
       <c r="B32" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>125802866</v>
       </c>
       <c r="B33" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>125802868</v>
       </c>
       <c r="B34" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>125799113</v>
       </c>
       <c r="B37" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,45 +4450,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125807835</v>
+        <v>125799913</v>
       </c>
       <c r="B38" t="n">
-        <v>79562</v>
+        <v>91203</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478334</v>
+        <v>478328</v>
       </c>
       <c r="R38" t="n">
-        <v>6950420</v>
+        <v>6950173</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4535,57 +4535,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125799913</v>
+        <v>125807835</v>
       </c>
       <c r="B39" t="n">
-        <v>91201</v>
+        <v>79562</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478328</v>
+        <v>478334</v>
       </c>
       <c r="R39" t="n">
-        <v>6950173</v>
+        <v>6950420</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4632,12 +4632,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125800087</v>
+        <v>125802854</v>
       </c>
       <c r="B41" t="n">
-        <v>91236</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478329</v>
+        <v>478350</v>
       </c>
       <c r="R41" t="n">
-        <v>6950196</v>
+        <v>6950427</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,9 +4819,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4836,22 +4846,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125802854</v>
+        <v>125800087</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>91238</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4859,37 +4869,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478350</v>
+        <v>478329</v>
       </c>
       <c r="R42" t="n">
-        <v>6950427</v>
+        <v>6950196</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4916,19 +4926,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,12 +4943,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4958,7 +4958,7 @@
         <v>125802877</v>
       </c>
       <c r="B43" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802878</v>
+        <v>125802883</v>
       </c>
       <c r="B45" t="n">
-        <v>91532</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478404</v>
+        <v>478412</v>
       </c>
       <c r="R45" t="n">
-        <v>6950178</v>
+        <v>6950164</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125802862</v>
+        <v>125802878</v>
       </c>
       <c r="B46" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478280</v>
+        <v>478404</v>
       </c>
       <c r="R46" t="n">
-        <v>6950247</v>
+        <v>6950178</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802863</v>
+        <v>125802862</v>
       </c>
       <c r="B47" t="n">
-        <v>91236</v>
+        <v>91534</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478273</v>
+        <v>478280</v>
       </c>
       <c r="R47" t="n">
-        <v>6950245</v>
+        <v>6950247</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125802883</v>
+        <v>125802863</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>91238</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478412</v>
+        <v>478273</v>
       </c>
       <c r="R48" t="n">
-        <v>6950164</v>
+        <v>6950245</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5804,7 +5804,7 @@
         <v>125799056</v>
       </c>
       <c r="B51" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125800061</v>
+        <v>125802855</v>
       </c>
       <c r="B52" t="n">
-        <v>91532</v>
+        <v>78379</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5909,37 +5909,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478319</v>
+        <v>478311</v>
       </c>
       <c r="R52" t="n">
-        <v>6950199</v>
+        <v>6950419</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5966,9 +5966,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5983,12 +5993,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6092,10 +6102,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125802855</v>
+        <v>125800061</v>
       </c>
       <c r="B54" t="n">
-        <v>78379</v>
+        <v>91534</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6103,37 +6113,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478311</v>
+        <v>478319</v>
       </c>
       <c r="R54" t="n">
-        <v>6950419</v>
+        <v>6950199</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6160,19 +6170,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6187,12 +6187,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6202,7 +6202,7 @@
         <v>125802870</v>
       </c>
       <c r="B55" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6306,32 +6306,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125799789</v>
+        <v>125800829</v>
       </c>
       <c r="B56" t="n">
-        <v>91250</v>
+        <v>91598</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>2063</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478279</v>
+        <v>478489</v>
       </c>
       <c r="R56" t="n">
-        <v>6950281</v>
+        <v>6950236</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6374,19 +6374,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6401,44 +6391,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125795897</v>
+        <v>125799789</v>
       </c>
       <c r="B57" t="n">
-        <v>91690</v>
+        <v>91252</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6448,13 +6438,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478293</v>
+        <v>478279</v>
       </c>
       <c r="R57" t="n">
-        <v>6950485</v>
+        <v>6950281</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6481,9 +6471,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6498,22 +6498,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125800829</v>
+        <v>125795897</v>
       </c>
       <c r="B58" t="n">
-        <v>91596</v>
+        <v>91692</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2063</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478489</v>
+        <v>478293</v>
       </c>
       <c r="R58" t="n">
-        <v>6950236</v>
+        <v>6950485</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6714,48 +6714,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125807837</v>
+        <v>125802875</v>
       </c>
       <c r="B60" t="n">
-        <v>91933</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478281</v>
+        <v>478367</v>
       </c>
       <c r="R60" t="n">
-        <v>6950244</v>
+        <v>6950197</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6782,9 +6782,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6799,60 +6809,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125802875</v>
+        <v>125807837</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>91935</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478367</v>
+        <v>478281</v>
       </c>
       <c r="R61" t="n">
-        <v>6950197</v>
+        <v>6950244</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6879,19 +6889,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6906,12 +6906,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7125,7 +7125,7 @@
         <v>125833009</v>
       </c>
       <c r="B64" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125833015</v>
+        <v>125833008</v>
       </c>
       <c r="B66" t="n">
-        <v>57652</v>
+        <v>91238</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7332,21 +7332,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478373</v>
+        <v>478314</v>
       </c>
       <c r="R66" t="n">
-        <v>6950375</v>
+        <v>6950373</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7392,11 +7392,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7423,10 +7418,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125833008</v>
+        <v>125833015</v>
       </c>
       <c r="B67" t="n">
-        <v>91236</v>
+        <v>57652</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7434,21 +7429,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7458,10 +7453,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478314</v>
+        <v>478373</v>
       </c>
       <c r="R67" t="n">
-        <v>6950373</v>
+        <v>6950375</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7494,6 +7489,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7523,7 +7523,7 @@
         <v>125833006</v>
       </c>
       <c r="B68" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>125833018</v>
       </c>
       <c r="B69" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>125833007</v>
       </c>
       <c r="B70" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>125799318</v>
       </c>
       <c r="B72" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -3614,48 +3614,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125802884</v>
+        <v>125799882</v>
       </c>
       <c r="B30" t="n">
-        <v>98366</v>
+        <v>91238</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478449</v>
+        <v>478301</v>
       </c>
       <c r="R30" t="n">
-        <v>6950182</v>
+        <v>6950180</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3709,60 +3709,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125799882</v>
+        <v>125802884</v>
       </c>
       <c r="B31" t="n">
-        <v>91238</v>
+        <v>98366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478301</v>
+        <v>478449</v>
       </c>
       <c r="R31" t="n">
-        <v>6950180</v>
+        <v>6950182</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3816,12 +3816,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4353,32 +4353,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125799113</v>
+        <v>125799913</v>
       </c>
       <c r="B37" t="n">
-        <v>91534</v>
+        <v>91203</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478286</v>
+        <v>478328</v>
       </c>
       <c r="R37" t="n">
-        <v>6950325</v>
+        <v>6950173</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4450,32 +4450,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125799913</v>
+        <v>125799113</v>
       </c>
       <c r="B38" t="n">
-        <v>91203</v>
+        <v>91534</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478328</v>
+        <v>478286</v>
       </c>
       <c r="R38" t="n">
-        <v>6950173</v>
+        <v>6950325</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5801,45 +5801,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125799056</v>
+        <v>125802870</v>
       </c>
       <c r="B51" t="n">
-        <v>91238</v>
+        <v>98366</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478298</v>
+        <v>478330</v>
       </c>
       <c r="R51" t="n">
-        <v>6950374</v>
+        <v>6950181</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5869,9 +5869,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5886,12 +5896,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6102,10 +6112,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125800061</v>
+        <v>125799056</v>
       </c>
       <c r="B54" t="n">
-        <v>91534</v>
+        <v>91238</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6113,21 +6123,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6137,10 +6147,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478319</v>
+        <v>478298</v>
       </c>
       <c r="R54" t="n">
-        <v>6950199</v>
+        <v>6950374</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6199,45 +6209,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125802870</v>
+        <v>125800061</v>
       </c>
       <c r="B55" t="n">
-        <v>98366</v>
+        <v>91534</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478330</v>
+        <v>478319</v>
       </c>
       <c r="R55" t="n">
-        <v>6950181</v>
+        <v>6950199</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6267,19 +6277,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6294,12 +6294,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -2682,7 +2682,7 @@
         <v>125657692</v>
       </c>
       <c r="B21" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>125657691</v>
       </c>
       <c r="B22" t="n">
-        <v>57756</v>
+        <v>57760</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>125798806</v>
       </c>
       <c r="B23" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>125800103</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>125800701</v>
       </c>
       <c r="B25" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125802853</v>
+        <v>125807839</v>
       </c>
       <c r="B26" t="n">
-        <v>78379</v>
+        <v>78644</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,37 +3208,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478364</v>
+        <v>478450</v>
       </c>
       <c r="R26" t="n">
-        <v>6950434</v>
+        <v>6950228</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3265,19 +3265,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3292,22 +3282,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125807839</v>
+        <v>125802853</v>
       </c>
       <c r="B27" t="n">
-        <v>78640</v>
+        <v>78383</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3315,37 +3305,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478450</v>
+        <v>478364</v>
       </c>
       <c r="R27" t="n">
-        <v>6950228</v>
+        <v>6950434</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3372,9 +3362,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3389,12 +3389,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3404,7 +3404,7 @@
         <v>125799925</v>
       </c>
       <c r="B28" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>125808994</v>
       </c>
       <c r="B29" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>125799882</v>
       </c>
       <c r="B30" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>125802884</v>
       </c>
       <c r="B31" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>125799436</v>
       </c>
       <c r="B32" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>125802866</v>
       </c>
       <c r="B33" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>125802868</v>
       </c>
       <c r="B34" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>125802861</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>125802887</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4353,45 +4353,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125799913</v>
+        <v>125807835</v>
       </c>
       <c r="B37" t="n">
-        <v>91203</v>
+        <v>79566</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478328</v>
+        <v>478334</v>
       </c>
       <c r="R37" t="n">
-        <v>6950173</v>
+        <v>6950420</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4438,12 +4438,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4453,7 +4453,7 @@
         <v>125799113</v>
       </c>
       <c r="B38" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4547,45 +4547,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125807835</v>
+        <v>125799913</v>
       </c>
       <c r="B39" t="n">
-        <v>79562</v>
+        <v>91207</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478334</v>
+        <v>478328</v>
       </c>
       <c r="R39" t="n">
-        <v>6950420</v>
+        <v>6950173</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4632,12 +4632,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4647,7 +4647,7 @@
         <v>125802871</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>125802854</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>125800087</v>
       </c>
       <c r="B42" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>125802877</v>
       </c>
       <c r="B43" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5062,10 +5062,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125797150</v>
+        <v>125802883</v>
       </c>
       <c r="B44" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5073,42 +5073,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478393</v>
+        <v>478412</v>
       </c>
       <c r="R44" t="n">
-        <v>6950404</v>
+        <v>6950164</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5135,14 +5130,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5157,22 +5157,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802883</v>
+        <v>125802862</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>91538</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478412</v>
+        <v>478280</v>
       </c>
       <c r="R45" t="n">
-        <v>6950164</v>
+        <v>6950247</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125802878</v>
+        <v>125797150</v>
       </c>
       <c r="B46" t="n">
-        <v>91534</v>
+        <v>57656</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,37 +5287,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478404</v>
+        <v>478393</v>
       </c>
       <c r="R46" t="n">
-        <v>6950178</v>
+        <v>6950404</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5344,19 +5349,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:15</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5371,22 +5371,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802862</v>
+        <v>125802878</v>
       </c>
       <c r="B47" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478280</v>
+        <v>478404</v>
       </c>
       <c r="R47" t="n">
-        <v>6950247</v>
+        <v>6950178</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5493,7 +5493,7 @@
         <v>125802863</v>
       </c>
       <c r="B48" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125807838</v>
+        <v>125802867</v>
       </c>
       <c r="B49" t="n">
-        <v>79052</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5608,37 +5608,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478276</v>
+        <v>478281</v>
       </c>
       <c r="R49" t="n">
-        <v>6950250</v>
+        <v>6950219</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5665,9 +5665,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5682,22 +5692,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125802867</v>
+        <v>125807838</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>79056</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5705,37 +5715,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478281</v>
+        <v>478276</v>
       </c>
       <c r="R50" t="n">
-        <v>6950219</v>
+        <v>6950250</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5762,19 +5772,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5789,57 +5789,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802870</v>
+        <v>125799056</v>
       </c>
       <c r="B51" t="n">
-        <v>98366</v>
+        <v>91242</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478330</v>
+        <v>478298</v>
       </c>
       <c r="R51" t="n">
-        <v>6950181</v>
+        <v>6950374</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5869,19 +5869,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5896,22 +5886,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802855</v>
+        <v>125800061</v>
       </c>
       <c r="B52" t="n">
-        <v>78379</v>
+        <v>91538</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5919,37 +5909,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478311</v>
+        <v>478319</v>
       </c>
       <c r="R52" t="n">
-        <v>6950419</v>
+        <v>6950199</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5976,19 +5966,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6003,57 +5983,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125807840</v>
+        <v>125802870</v>
       </c>
       <c r="B53" t="n">
-        <v>78379</v>
+        <v>98370</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478314</v>
+        <v>478330</v>
       </c>
       <c r="R53" t="n">
-        <v>6950423</v>
+        <v>6950181</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6083,9 +6063,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6100,22 +6090,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125799056</v>
+        <v>125807840</v>
       </c>
       <c r="B54" t="n">
-        <v>91238</v>
+        <v>78383</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6123,34 +6113,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478298</v>
+        <v>478314</v>
       </c>
       <c r="R54" t="n">
-        <v>6950374</v>
+        <v>6950423</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6197,22 +6187,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125800061</v>
+        <v>125802855</v>
       </c>
       <c r="B55" t="n">
-        <v>91534</v>
+        <v>78383</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6220,37 +6210,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478319</v>
+        <v>478311</v>
       </c>
       <c r="R55" t="n">
-        <v>6950199</v>
+        <v>6950419</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6277,9 +6267,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6294,22 +6294,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125800829</v>
+        <v>125795897</v>
       </c>
       <c r="B56" t="n">
-        <v>91598</v>
+        <v>91696</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6317,21 +6317,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2063</v>
+        <v>1209</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478489</v>
+        <v>478293</v>
       </c>
       <c r="R56" t="n">
-        <v>6950236</v>
+        <v>6950485</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6406,7 +6406,7 @@
         <v>125799789</v>
       </c>
       <c r="B57" t="n">
-        <v>91252</v>
+        <v>91256</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6510,10 +6510,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125795897</v>
+        <v>125800829</v>
       </c>
       <c r="B58" t="n">
-        <v>91692</v>
+        <v>91602</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>2063</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478293</v>
+        <v>478489</v>
       </c>
       <c r="R58" t="n">
-        <v>6950485</v>
+        <v>6950236</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6610,7 +6610,7 @@
         <v>125802858</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6714,48 +6714,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125802875</v>
+        <v>125807837</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>91939</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478367</v>
+        <v>478281</v>
       </c>
       <c r="R60" t="n">
-        <v>6950197</v>
+        <v>6950244</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6782,19 +6782,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6809,60 +6799,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125807837</v>
+        <v>125802875</v>
       </c>
       <c r="B61" t="n">
-        <v>91935</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478281</v>
+        <v>478367</v>
       </c>
       <c r="R61" t="n">
-        <v>6950244</v>
+        <v>6950197</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6889,9 +6879,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6906,12 +6906,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6921,7 +6921,7 @@
         <v>125802859</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>125797369</v>
       </c>
       <c r="B63" t="n">
-        <v>78997</v>
+        <v>79001</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>125833009</v>
       </c>
       <c r="B64" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>125833014</v>
       </c>
       <c r="B65" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125833008</v>
+        <v>125833015</v>
       </c>
       <c r="B66" t="n">
-        <v>91238</v>
+        <v>57656</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7332,21 +7332,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478314</v>
+        <v>478373</v>
       </c>
       <c r="R66" t="n">
-        <v>6950373</v>
+        <v>6950375</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7392,6 +7392,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7418,10 +7423,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125833015</v>
+        <v>125833008</v>
       </c>
       <c r="B67" t="n">
-        <v>57652</v>
+        <v>91242</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7429,21 +7434,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7453,10 +7458,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478373</v>
+        <v>478314</v>
       </c>
       <c r="R67" t="n">
-        <v>6950375</v>
+        <v>6950373</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7489,11 +7494,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7523,7 +7523,7 @@
         <v>125833006</v>
       </c>
       <c r="B68" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>125833018</v>
       </c>
       <c r="B69" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>125833007</v>
       </c>
       <c r="B70" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>125833013</v>
       </c>
       <c r="B71" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>125799318</v>
       </c>
       <c r="B72" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -3828,48 +3828,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125799436</v>
+        <v>125802866</v>
       </c>
       <c r="B32" t="n">
-        <v>91696</v>
+        <v>91538</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
         <v>478281</v>
       </c>
       <c r="R32" t="n">
-        <v>6950242</v>
+        <v>6950219</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3896,9 +3896,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3913,44 +3923,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125802866</v>
+        <v>125802868</v>
       </c>
       <c r="B33" t="n">
-        <v>91538</v>
+        <v>98370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3960,10 +3970,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478281</v>
+        <v>478280</v>
       </c>
       <c r="R33" t="n">
-        <v>6950219</v>
+        <v>6950190</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -3995,7 +4005,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4005,7 +4015,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4032,48 +4042,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125802868</v>
+        <v>125799436</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>91696</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478280</v>
+        <v>478281</v>
       </c>
       <c r="R34" t="n">
-        <v>6950190</v>
+        <v>6950242</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4100,19 +4110,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4127,12 +4127,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5801,10 +5801,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125799056</v>
+        <v>125800061</v>
       </c>
       <c r="B51" t="n">
-        <v>91242</v>
+        <v>91538</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5812,21 +5812,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478298</v>
+        <v>478319</v>
       </c>
       <c r="R51" t="n">
-        <v>6950374</v>
+        <v>6950199</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5898,45 +5898,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125800061</v>
+        <v>125802870</v>
       </c>
       <c r="B52" t="n">
-        <v>91538</v>
+        <v>98370</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478319</v>
+        <v>478330</v>
       </c>
       <c r="R52" t="n">
-        <v>6950199</v>
+        <v>6950181</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5966,9 +5966,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5983,57 +5993,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125802870</v>
+        <v>125799056</v>
       </c>
       <c r="B53" t="n">
-        <v>98370</v>
+        <v>91242</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478330</v>
+        <v>478298</v>
       </c>
       <c r="R53" t="n">
-        <v>6950181</v>
+        <v>6950374</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6063,19 +6073,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6090,12 +6090,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125833015</v>
+        <v>125833008</v>
       </c>
       <c r="B66" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7332,21 +7332,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478373</v>
+        <v>478314</v>
       </c>
       <c r="R66" t="n">
-        <v>6950375</v>
+        <v>6950373</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7392,11 +7392,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7423,10 +7418,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125833008</v>
+        <v>125833015</v>
       </c>
       <c r="B67" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7434,21 +7429,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7458,10 +7453,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478314</v>
+        <v>478373</v>
       </c>
       <c r="R67" t="n">
-        <v>6950373</v>
+        <v>6950375</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7494,6 +7489,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125807839</v>
+        <v>125802853</v>
       </c>
       <c r="B26" t="n">
-        <v>78644</v>
+        <v>78383</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,37 +3208,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478450</v>
+        <v>478364</v>
       </c>
       <c r="R26" t="n">
-        <v>6950228</v>
+        <v>6950434</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3265,9 +3265,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3282,22 +3292,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125802853</v>
+        <v>125807839</v>
       </c>
       <c r="B27" t="n">
-        <v>78383</v>
+        <v>78644</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3305,37 +3315,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478364</v>
+        <v>478450</v>
       </c>
       <c r="R27" t="n">
-        <v>6950434</v>
+        <v>6950228</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3362,19 +3372,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3389,60 +3389,64 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125799925</v>
+        <v>125808994</v>
       </c>
       <c r="B28" t="n">
-        <v>91696</v>
+        <v>57656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Klippberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478282</v>
+        <v>478416</v>
       </c>
       <c r="R28" t="n">
-        <v>6950251</v>
+        <v>6950415</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3469,19 +3473,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:04</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3496,64 +3495,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125808994</v>
+        <v>125799925</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>91696</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Klippberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478416</v>
+        <v>478282</v>
       </c>
       <c r="R29" t="n">
-        <v>6950415</v>
+        <v>6950251</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3580,14 +3575,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3602,12 +3602,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3724,7 +3724,7 @@
         <v>125802884</v>
       </c>
       <c r="B31" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3828,48 +3828,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125802866</v>
+        <v>125799436</v>
       </c>
       <c r="B32" t="n">
-        <v>91538</v>
+        <v>91696</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
         <v>478281</v>
       </c>
       <c r="R32" t="n">
-        <v>6950219</v>
+        <v>6950242</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3896,19 +3896,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3923,12 +3913,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3938,7 +3928,7 @@
         <v>125802868</v>
       </c>
       <c r="B33" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4042,48 +4032,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125799436</v>
+        <v>125802866</v>
       </c>
       <c r="B34" t="n">
-        <v>91696</v>
+        <v>91538</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
         <v>478281</v>
       </c>
       <c r="R34" t="n">
-        <v>6950242</v>
+        <v>6950219</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4110,9 +4100,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4127,12 +4127,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125807835</v>
+        <v>125799113</v>
       </c>
       <c r="B37" t="n">
-        <v>79566</v>
+        <v>91538</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4364,34 +4364,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478334</v>
+        <v>478286</v>
       </c>
       <c r="R37" t="n">
-        <v>6950420</v>
+        <v>6950325</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4438,44 +4438,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125799113</v>
+        <v>125799913</v>
       </c>
       <c r="B38" t="n">
-        <v>91538</v>
+        <v>91207</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478286</v>
+        <v>478328</v>
       </c>
       <c r="R38" t="n">
-        <v>6950325</v>
+        <v>6950173</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4547,45 +4547,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125799913</v>
+        <v>125807835</v>
       </c>
       <c r="B39" t="n">
-        <v>91207</v>
+        <v>79566</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478328</v>
+        <v>478334</v>
       </c>
       <c r="R39" t="n">
-        <v>6950173</v>
+        <v>6950420</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4632,12 +4632,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4955,32 +4955,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125802877</v>
+        <v>125802878</v>
       </c>
       <c r="B43" t="n">
-        <v>98370</v>
+        <v>91538</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478396</v>
+        <v>478404</v>
       </c>
       <c r="R43" t="n">
-        <v>6950183</v>
+        <v>6950178</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5062,10 +5062,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125802883</v>
+        <v>125802862</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>91538</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478412</v>
+        <v>478280</v>
       </c>
       <c r="R44" t="n">
-        <v>6950164</v>
+        <v>6950247</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802862</v>
+        <v>125802863</v>
       </c>
       <c r="B45" t="n">
-        <v>91538</v>
+        <v>91242</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478280</v>
+        <v>478273</v>
       </c>
       <c r="R45" t="n">
-        <v>6950247</v>
+        <v>6950245</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802878</v>
+        <v>125802883</v>
       </c>
       <c r="B47" t="n">
-        <v>91538</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478404</v>
+        <v>478412</v>
       </c>
       <c r="R47" t="n">
-        <v>6950178</v>
+        <v>6950164</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125802863</v>
+        <v>125802877</v>
       </c>
       <c r="B48" t="n">
-        <v>91242</v>
+        <v>98373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478273</v>
+        <v>478396</v>
       </c>
       <c r="R48" t="n">
-        <v>6950245</v>
+        <v>6950183</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5801,10 +5801,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125800061</v>
+        <v>125799056</v>
       </c>
       <c r="B51" t="n">
-        <v>91538</v>
+        <v>91242</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5812,21 +5812,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478319</v>
+        <v>478298</v>
       </c>
       <c r="R51" t="n">
-        <v>6950199</v>
+        <v>6950374</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5898,32 +5898,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802870</v>
+        <v>125802855</v>
       </c>
       <c r="B52" t="n">
-        <v>98370</v>
+        <v>78383</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5933,13 +5933,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478330</v>
+        <v>478311</v>
       </c>
       <c r="R52" t="n">
-        <v>6950181</v>
+        <v>6950419</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6005,10 +6005,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125799056</v>
+        <v>125807840</v>
       </c>
       <c r="B53" t="n">
-        <v>91242</v>
+        <v>78383</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6016,34 +6016,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478298</v>
+        <v>478314</v>
       </c>
       <c r="R53" t="n">
-        <v>6950374</v>
+        <v>6950423</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6090,22 +6090,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125807840</v>
+        <v>125800061</v>
       </c>
       <c r="B54" t="n">
-        <v>78383</v>
+        <v>91538</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6113,34 +6113,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478314</v>
+        <v>478319</v>
       </c>
       <c r="R54" t="n">
-        <v>6950423</v>
+        <v>6950199</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6187,44 +6187,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125802855</v>
+        <v>125802870</v>
       </c>
       <c r="B55" t="n">
-        <v>78383</v>
+        <v>98373</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6234,13 +6234,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478311</v>
+        <v>478330</v>
       </c>
       <c r="R55" t="n">
-        <v>6950419</v>
+        <v>6950181</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6306,10 +6306,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125795897</v>
+        <v>125800829</v>
       </c>
       <c r="B56" t="n">
-        <v>91696</v>
+        <v>91602</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6317,21 +6317,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1209</v>
+        <v>2063</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478293</v>
+        <v>478489</v>
       </c>
       <c r="R56" t="n">
-        <v>6950485</v>
+        <v>6950236</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6510,10 +6510,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125800829</v>
+        <v>125795897</v>
       </c>
       <c r="B58" t="n">
-        <v>91602</v>
+        <v>91696</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2063</v>
+        <v>1209</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478489</v>
+        <v>478293</v>
       </c>
       <c r="R58" t="n">
-        <v>6950236</v>
+        <v>6950485</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6714,48 +6714,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125807837</v>
+        <v>125802875</v>
       </c>
       <c r="B60" t="n">
-        <v>91939</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478281</v>
+        <v>478367</v>
       </c>
       <c r="R60" t="n">
-        <v>6950244</v>
+        <v>6950197</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6782,9 +6782,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6799,60 +6809,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125802875</v>
+        <v>125807837</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>91939</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478367</v>
+        <v>478281</v>
       </c>
       <c r="R61" t="n">
-        <v>6950197</v>
+        <v>6950244</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6879,19 +6889,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6906,12 +6906,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7917,7 +7917,7 @@
         <v>125799318</v>
       </c>
       <c r="B72" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -2891,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125798806</v>
+        <v>125800103</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,21 +2902,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478289</v>
+        <v>478279</v>
       </c>
       <c r="R23" t="n">
-        <v>6950427</v>
+        <v>6950281</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2959,9 +2959,24 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,22 +2991,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125800103</v>
+        <v>125798806</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,21 +3014,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3023,13 +3038,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478279</v>
+        <v>478289</v>
       </c>
       <c r="R24" t="n">
-        <v>6950281</v>
+        <v>6950427</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3056,24 +3071,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3088,12 +3088,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125802853</v>
+        <v>125807839</v>
       </c>
       <c r="B26" t="n">
-        <v>78383</v>
+        <v>78644</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,37 +3208,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478364</v>
+        <v>478450</v>
       </c>
       <c r="R26" t="n">
-        <v>6950434</v>
+        <v>6950228</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3265,19 +3265,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3292,22 +3282,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125807839</v>
+        <v>125802853</v>
       </c>
       <c r="B27" t="n">
-        <v>78644</v>
+        <v>78383</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3315,37 +3305,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478450</v>
+        <v>478364</v>
       </c>
       <c r="R27" t="n">
-        <v>6950228</v>
+        <v>6950434</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3372,9 +3362,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3389,12 +3389,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3828,48 +3828,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125799436</v>
+        <v>125802868</v>
       </c>
       <c r="B32" t="n">
-        <v>91696</v>
+        <v>98373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478281</v>
+        <v>478280</v>
       </c>
       <c r="R32" t="n">
-        <v>6950242</v>
+        <v>6950190</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3896,9 +3896,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3913,60 +3923,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125802868</v>
+        <v>125799436</v>
       </c>
       <c r="B33" t="n">
-        <v>98373</v>
+        <v>91696</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478280</v>
+        <v>478281</v>
       </c>
       <c r="R33" t="n">
-        <v>6950190</v>
+        <v>6950242</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3993,19 +4003,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4020,12 +4020,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4955,32 +4955,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125802878</v>
+        <v>125802877</v>
       </c>
       <c r="B43" t="n">
-        <v>91538</v>
+        <v>98373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478404</v>
+        <v>478396</v>
       </c>
       <c r="R43" t="n">
-        <v>6950178</v>
+        <v>6950183</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5062,10 +5062,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125802862</v>
+        <v>125797150</v>
       </c>
       <c r="B44" t="n">
-        <v>91538</v>
+        <v>57656</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5073,37 +5073,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478280</v>
+        <v>478393</v>
       </c>
       <c r="R44" t="n">
-        <v>6950247</v>
+        <v>6950404</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5130,19 +5135,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:50</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5157,22 +5157,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802863</v>
+        <v>125802878</v>
       </c>
       <c r="B45" t="n">
-        <v>91242</v>
+        <v>91538</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478273</v>
+        <v>478404</v>
       </c>
       <c r="R45" t="n">
-        <v>6950245</v>
+        <v>6950178</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125797150</v>
+        <v>125802862</v>
       </c>
       <c r="B46" t="n">
-        <v>57656</v>
+        <v>91538</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,42 +5287,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478393</v>
+        <v>478280</v>
       </c>
       <c r="R46" t="n">
-        <v>6950404</v>
+        <v>6950247</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5349,14 +5344,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5371,22 +5371,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802883</v>
+        <v>125802863</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478412</v>
+        <v>478273</v>
       </c>
       <c r="R47" t="n">
-        <v>6950164</v>
+        <v>6950245</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125802877</v>
+        <v>125802883</v>
       </c>
       <c r="B48" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478396</v>
+        <v>478412</v>
       </c>
       <c r="R48" t="n">
-        <v>6950183</v>
+        <v>6950164</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7321,10 +7321,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125833008</v>
+        <v>125833015</v>
       </c>
       <c r="B66" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7332,21 +7332,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478314</v>
+        <v>478373</v>
       </c>
       <c r="R66" t="n">
-        <v>6950373</v>
+        <v>6950375</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7392,6 +7392,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7418,10 +7423,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125833015</v>
+        <v>125833008</v>
       </c>
       <c r="B67" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7429,21 +7434,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7453,10 +7458,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478373</v>
+        <v>478314</v>
       </c>
       <c r="R67" t="n">
-        <v>6950375</v>
+        <v>6950373</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7489,11 +7494,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -3828,32 +3828,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125802868</v>
+        <v>125802866</v>
       </c>
       <c r="B32" t="n">
-        <v>98373</v>
+        <v>91538</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478280</v>
+        <v>478281</v>
       </c>
       <c r="R32" t="n">
-        <v>6950190</v>
+        <v>6950219</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3935,48 +3935,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125799436</v>
+        <v>125802868</v>
       </c>
       <c r="B33" t="n">
-        <v>91696</v>
+        <v>98373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478281</v>
+        <v>478280</v>
       </c>
       <c r="R33" t="n">
-        <v>6950242</v>
+        <v>6950190</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4003,9 +4003,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4020,60 +4030,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125802866</v>
+        <v>125799436</v>
       </c>
       <c r="B34" t="n">
-        <v>91538</v>
+        <v>91696</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
         <v>478281</v>
       </c>
       <c r="R34" t="n">
-        <v>6950219</v>
+        <v>6950242</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4100,19 +4110,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4127,12 +4127,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4353,32 +4353,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125799113</v>
+        <v>125799913</v>
       </c>
       <c r="B37" t="n">
-        <v>91538</v>
+        <v>91207</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478286</v>
+        <v>478328</v>
       </c>
       <c r="R37" t="n">
-        <v>6950325</v>
+        <v>6950173</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4450,32 +4450,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125799913</v>
+        <v>125799113</v>
       </c>
       <c r="B38" t="n">
-        <v>91207</v>
+        <v>91538</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478328</v>
+        <v>478286</v>
       </c>
       <c r="R38" t="n">
-        <v>6950173</v>
+        <v>6950325</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125802854</v>
+        <v>125800087</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478350</v>
+        <v>478329</v>
       </c>
       <c r="R41" t="n">
-        <v>6950427</v>
+        <v>6950196</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,19 +4819,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4846,22 +4836,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125800087</v>
+        <v>125802854</v>
       </c>
       <c r="B42" t="n">
-        <v>91242</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4869,37 +4859,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478329</v>
+        <v>478350</v>
       </c>
       <c r="R42" t="n">
-        <v>6950196</v>
+        <v>6950427</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4926,9 +4916,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,44 +4943,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125802877</v>
+        <v>125802883</v>
       </c>
       <c r="B43" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478396</v>
+        <v>478412</v>
       </c>
       <c r="R43" t="n">
-        <v>6950183</v>
+        <v>6950164</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125802883</v>
+        <v>125802877</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478412</v>
+        <v>478396</v>
       </c>
       <c r="R48" t="n">
-        <v>6950164</v>
+        <v>6950183</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5597,10 +5597,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125802867</v>
+        <v>125807838</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>79056</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5608,37 +5608,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478281</v>
+        <v>478276</v>
       </c>
       <c r="R49" t="n">
-        <v>6950219</v>
+        <v>6950250</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5665,19 +5665,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5692,22 +5682,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125807838</v>
+        <v>125802867</v>
       </c>
       <c r="B50" t="n">
-        <v>79056</v>
+        <v>78977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5715,37 +5705,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478276</v>
+        <v>478281</v>
       </c>
       <c r="R50" t="n">
-        <v>6950250</v>
+        <v>6950219</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5772,9 +5762,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5789,12 +5789,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5898,32 +5898,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802855</v>
+        <v>125802870</v>
       </c>
       <c r="B52" t="n">
-        <v>78383</v>
+        <v>98373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5933,13 +5933,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478311</v>
+        <v>478330</v>
       </c>
       <c r="R52" t="n">
-        <v>6950419</v>
+        <v>6950181</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6005,10 +6005,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125807840</v>
+        <v>125800061</v>
       </c>
       <c r="B53" t="n">
-        <v>78383</v>
+        <v>91538</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6016,34 +6016,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478314</v>
+        <v>478319</v>
       </c>
       <c r="R53" t="n">
-        <v>6950423</v>
+        <v>6950199</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6090,22 +6090,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125800061</v>
+        <v>125802855</v>
       </c>
       <c r="B54" t="n">
-        <v>91538</v>
+        <v>78383</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6113,37 +6113,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478319</v>
+        <v>478311</v>
       </c>
       <c r="R54" t="n">
-        <v>6950199</v>
+        <v>6950419</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6170,9 +6170,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6187,57 +6197,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125802870</v>
+        <v>125807840</v>
       </c>
       <c r="B55" t="n">
-        <v>98373</v>
+        <v>78383</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478330</v>
+        <v>478314</v>
       </c>
       <c r="R55" t="n">
-        <v>6950181</v>
+        <v>6950423</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6267,19 +6277,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6294,44 +6294,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125800829</v>
+        <v>125799789</v>
       </c>
       <c r="B56" t="n">
-        <v>91602</v>
+        <v>91256</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2063</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478489</v>
+        <v>478279</v>
       </c>
       <c r="R56" t="n">
-        <v>6950236</v>
+        <v>6950281</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6374,9 +6374,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6391,44 +6401,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125799789</v>
+        <v>125795897</v>
       </c>
       <c r="B57" t="n">
-        <v>91256</v>
+        <v>91696</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6438,13 +6448,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478279</v>
+        <v>478293</v>
       </c>
       <c r="R57" t="n">
-        <v>6950281</v>
+        <v>6950485</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6471,19 +6481,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6498,22 +6498,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125795897</v>
+        <v>125800829</v>
       </c>
       <c r="B58" t="n">
-        <v>91696</v>
+        <v>91602</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>2063</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478293</v>
+        <v>478489</v>
       </c>
       <c r="R58" t="n">
-        <v>6950485</v>
+        <v>6950236</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6714,48 +6714,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125802875</v>
+        <v>125807837</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>91939</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478367</v>
+        <v>478281</v>
       </c>
       <c r="R60" t="n">
-        <v>6950197</v>
+        <v>6950244</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6782,19 +6782,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6809,60 +6799,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125807837</v>
+        <v>125802875</v>
       </c>
       <c r="B61" t="n">
-        <v>91939</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478281</v>
+        <v>478367</v>
       </c>
       <c r="R61" t="n">
-        <v>6950244</v>
+        <v>6950197</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6889,9 +6879,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6906,12 +6906,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -5062,53 +5062,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125797150</v>
+        <v>125802877</v>
       </c>
       <c r="B44" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478393</v>
+        <v>478396</v>
       </c>
       <c r="R44" t="n">
-        <v>6950404</v>
+        <v>6950183</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5135,14 +5130,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5157,22 +5157,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125802878</v>
+        <v>125797150</v>
       </c>
       <c r="B45" t="n">
-        <v>91538</v>
+        <v>57656</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,37 +5180,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478404</v>
+        <v>478393</v>
       </c>
       <c r="R45" t="n">
-        <v>6950178</v>
+        <v>6950404</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5237,19 +5242,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:15</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5264,19 +5264,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125802862</v>
+        <v>125802878</v>
       </c>
       <c r="B46" t="n">
         <v>91538</v>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478280</v>
+        <v>478404</v>
       </c>
       <c r="R46" t="n">
-        <v>6950247</v>
+        <v>6950178</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802863</v>
+        <v>125802862</v>
       </c>
       <c r="B47" t="n">
-        <v>91242</v>
+        <v>91538</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478273</v>
+        <v>478280</v>
       </c>
       <c r="R47" t="n">
-        <v>6950245</v>
+        <v>6950247</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5490,32 +5490,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125802877</v>
+        <v>125802863</v>
       </c>
       <c r="B48" t="n">
-        <v>98373</v>
+        <v>91242</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478396</v>
+        <v>478273</v>
       </c>
       <c r="R48" t="n">
-        <v>6950183</v>
+        <v>6950245</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 44835-2024 artfynd.xlsx
+++ b/artfynd/A 44835-2024 artfynd.xlsx
@@ -2894,7 +2894,7 @@
         <v>125800103</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>125798806</v>
       </c>
       <c r="B24" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>125800701</v>
       </c>
       <c r="B25" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>125807839</v>
       </c>
       <c r="B26" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>125802853</v>
       </c>
       <c r="B27" t="n">
-        <v>78383</v>
+        <v>78386</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>125808994</v>
       </c>
       <c r="B28" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>125799925</v>
       </c>
       <c r="B29" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>125799882</v>
       </c>
       <c r="B30" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>125802884</v>
       </c>
       <c r="B31" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>125802866</v>
       </c>
       <c r="B32" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>125802868</v>
       </c>
       <c r="B33" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>125799436</v>
       </c>
       <c r="B34" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>125802861</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>125802887</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4353,45 +4353,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125799913</v>
+        <v>125807835</v>
       </c>
       <c r="B37" t="n">
-        <v>91207</v>
+        <v>79569</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478328</v>
+        <v>478334</v>
       </c>
       <c r="R37" t="n">
-        <v>6950173</v>
+        <v>6950420</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4438,12 +4438,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4453,7 +4453,7 @@
         <v>125799113</v>
       </c>
       <c r="B38" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4547,45 +4547,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125807835</v>
+        <v>125799913</v>
       </c>
       <c r="B39" t="n">
-        <v>79566</v>
+        <v>91210</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478334</v>
+        <v>478328</v>
       </c>
       <c r="R39" t="n">
-        <v>6950420</v>
+        <v>6950173</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4632,12 +4632,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4647,7 +4647,7 @@
         <v>125802871</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125800087</v>
+        <v>125802854</v>
       </c>
       <c r="B41" t="n">
-        <v>91242</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,37 +4762,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478329</v>
+        <v>478350</v>
       </c>
       <c r="R41" t="n">
-        <v>6950196</v>
+        <v>6950427</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,9 +4819,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4836,22 +4846,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125802854</v>
+        <v>125800087</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>91245</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4859,37 +4869,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478350</v>
+        <v>478329</v>
       </c>
       <c r="R42" t="n">
-        <v>6950427</v>
+        <v>6950196</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4916,19 +4926,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,22 +4943,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125802883</v>
+        <v>125802878</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>91541</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478412</v>
+        <v>478404</v>
       </c>
       <c r="R43" t="n">
-        <v>6950164</v>
+        <v>6950178</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5062,32 +5062,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125802877</v>
+        <v>125802862</v>
       </c>
       <c r="B44" t="n">
-        <v>98373</v>
+        <v>91541</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478396</v>
+        <v>478280</v>
       </c>
       <c r="R44" t="n">
-        <v>6950183</v>
+        <v>6950247</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125797150</v>
+        <v>125802863</v>
       </c>
       <c r="B45" t="n">
-        <v>57656</v>
+        <v>91245</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,42 +5180,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478393</v>
+        <v>478273</v>
       </c>
       <c r="R45" t="n">
-        <v>6950404</v>
+        <v>6950245</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5242,14 +5237,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5264,22 +5264,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125802878</v>
+        <v>125802883</v>
       </c>
       <c r="B46" t="n">
-        <v>91538</v>
+        <v>78980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478404</v>
+        <v>478412</v>
       </c>
       <c r="R46" t="n">
-        <v>6950178</v>
+        <v>6950164</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5383,32 +5383,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125802862</v>
+        <v>125802877</v>
       </c>
       <c r="B47" t="n">
-        <v>91538</v>
+        <v>98382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478280</v>
+        <v>478396</v>
       </c>
       <c r="R47" t="n">
-        <v>6950247</v>
+        <v>6950183</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125802863</v>
+        <v>125797150</v>
       </c>
       <c r="B48" t="n">
-        <v>91242</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5501,37 +5501,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478273</v>
+        <v>478393</v>
       </c>
       <c r="R48" t="n">
-        <v>6950245</v>
+        <v>6950404</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5558,19 +5563,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:55</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5585,12 +5585,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5600,7 +5600,7 @@
         <v>125807838</v>
       </c>
       <c r="B49" t="n">
-        <v>79056</v>
+        <v>79059</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>125802867</v>
       </c>
       <c r="B50" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,10 +5801,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125799056</v>
+        <v>125800061</v>
       </c>
       <c r="B51" t="n">
-        <v>91242</v>
+        <v>91541</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5812,21 +5812,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478298</v>
+        <v>478319</v>
       </c>
       <c r="R51" t="n">
-        <v>6950374</v>
+        <v>6950199</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5898,32 +5898,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802870</v>
+        <v>125802855</v>
       </c>
       <c r="B52" t="n">
-        <v>98373</v>
+        <v>78386</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5933,13 +5933,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478330</v>
+        <v>478311</v>
       </c>
       <c r="R52" t="n">
-        <v>6950181</v>
+        <v>6950419</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6005,10 +6005,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125800061</v>
+        <v>125807840</v>
       </c>
       <c r="B53" t="n">
-        <v>91538</v>
+        <v>78386</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6016,34 +6016,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Digerberget, Digerberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478319</v>
+        <v>478314</v>
       </c>
       <c r="R53" t="n">
-        <v>6950199</v>
+        <v>6950423</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6090,44 +6090,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125802855</v>
+        <v>125802870</v>
       </c>
       <c r="B54" t="n">
-        <v>78383</v>
+        <v>98382</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6137,13 +6137,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478311</v>
+        <v>478330</v>
       </c>
       <c r="R54" t="n">
-        <v>6950419</v>
+        <v>6950181</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6209,10 +6209,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125807840</v>
+        <v>125799056</v>
       </c>
       <c r="B55" t="n">
-        <v>78383</v>
+        <v>91245</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6220,34 +6220,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Digerberget, Digerberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478314</v>
+        <v>478298</v>
       </c>
       <c r="R55" t="n">
-        <v>6950423</v>
+        <v>6950374</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6294,12 +6294,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6309,7 +6309,7 @@
         <v>125799789</v>
       </c>
       <c r="B56" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>125795897</v>
       </c>
       <c r="B57" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>125800829</v>
       </c>
       <c r="B58" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>125802858</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>125807837</v>
       </c>
       <c r="B60" t="n">
-        <v>91939</v>
+        <v>91942</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>125802875</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>125802859</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>125797369</v>
       </c>
       <c r="B63" t="n">
-        <v>79001</v>
+        <v>79004</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>125833009</v>
       </c>
       <c r="B64" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>125833014</v>
       </c>
       <c r="B65" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125833015</v>
+        <v>125833008</v>
       </c>
       <c r="B66" t="n">
-        <v>57656</v>
+        <v>91245</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7332,21 +7332,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478373</v>
+        <v>478314</v>
       </c>
       <c r="R66" t="n">
-        <v>6950375</v>
+        <v>6950373</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7392,11 +7392,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7423,10 +7418,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125833008</v>
+        <v>125833015</v>
       </c>
       <c r="B67" t="n">
-        <v>91242</v>
+        <v>57657</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7434,21 +7429,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7458,10 +7453,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478314</v>
+        <v>478373</v>
       </c>
       <c r="R67" t="n">
-        <v>6950373</v>
+        <v>6950375</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7494,6 +7489,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7523,7 +7523,7 @@
         <v>125833006</v>
       </c>
       <c r="B68" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>125833018</v>
       </c>
       <c r="B69" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>125833007</v>
       </c>
       <c r="B70" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>125833013</v>
       </c>
       <c r="B71" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>125799318</v>
       </c>
       <c r="B72" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
